--- a/doc/en_US.xlsx
+++ b/doc/en_US.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QT\workSpace\BMSTOOL\bmsTool\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{4E405ACA-7AB6-4505-89C0-874789BC9214}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{97376734-4759-4065-93E5-3F92EC050994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" xr2:uid="{0978753C-B27B-4003-8041-63A09D5276AE}"/>
+    <workbookView xWindow="1755" yWindow="7335" windowWidth="23250" windowHeight="12810" xr2:uid="{C4F1E5FA-5995-4FB6-94E9-A8F7207975B8}"/>
   </bookViews>
   <sheets>
     <sheet name="en_US" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="269">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="267">
   <si>
     <t>Cell UV Alarm</t>
   </si>
@@ -70,7 +70,7 @@
     <t>Cell Voltage,U16,0.0001,0,V</t>
   </si>
   <si>
-    <t>Cell Fault Reversion</t>
+    <t>Cell Fault Clear</t>
   </si>
   <si>
     <t>Cell ID,U16,1,0,</t>
@@ -136,7 +136,7 @@
     <t>Module Temperature,I16,0.1,0,℃</t>
   </si>
   <si>
-    <t xml:space="preserve">Module Temperature Reversion </t>
+    <t xml:space="preserve">Module Temperature Fault Clear </t>
   </si>
   <si>
     <t>Module Temperature ID,U16,1,0,</t>
@@ -154,7 +154,7 @@
     <t>Pole OT Fault</t>
   </si>
   <si>
-    <t>Pole Fault Reversion</t>
+    <t>Pole Fault Clear</t>
   </si>
   <si>
     <t>Pole Temperature ID,U16,1,0,</t>
@@ -172,7 +172,7 @@
     <t>OC Fault</t>
   </si>
   <si>
-    <t>OC Reversion</t>
+    <t>OC Fault Clear</t>
   </si>
   <si>
     <t>Short-Circuit Fault</t>
@@ -193,7 +193,7 @@
     <t>String UV Fault</t>
   </si>
   <si>
-    <t>String Fault Reversion</t>
+    <t>String Fault Clear</t>
   </si>
   <si>
     <t>String INS Fault</t>
@@ -202,7 +202,7 @@
     <t>INS RES,U16,1,0,kΩ</t>
   </si>
   <si>
-    <t>String INS Fault Reversion</t>
+    <t>String INS Fault Clear</t>
   </si>
   <si>
     <t>String leakage Current Fault</t>
@@ -211,7 +211,7 @@
     <t>leakage Current,U16,1,0,mA</t>
   </si>
   <si>
-    <t>String leakage Current Fault Reversion</t>
+    <t>String leakage Current Fault Clear</t>
   </si>
   <si>
     <t xml:space="preserve">Begin CHG </t>
@@ -337,10 +337,10 @@
     <t>RTU Comm Fault</t>
   </si>
   <si>
-    <t>Cell Voltage Wire-Open Reversion</t>
-  </si>
-  <si>
-    <t>Temperature Wire-Open Reversion</t>
+    <t>Cell Voltage Wire-Open Clear</t>
+  </si>
+  <si>
+    <t>Temperature Wire-Open Clear</t>
   </si>
   <si>
     <t>String Pole OT Protection</t>
@@ -358,7 +358,7 @@
     <t>Temperature Wire-Open status,U16,1,0,</t>
   </si>
   <si>
-    <t>String Pole Reversion</t>
+    <t>String Pole Fault Clear</t>
   </si>
   <si>
     <t>Module Min /Max Temperature,U16,1,0,℃</t>
@@ -415,9 +415,6 @@
     <t>Voltage Wire-Open status,BIN,1,0,</t>
   </si>
   <si>
-    <t xml:space="preserve">Cell Fault Reversion </t>
-  </si>
-  <si>
     <t>Cell Max Voltage,U16,0.0001,0,V</t>
   </si>
   <si>
@@ -451,7 +448,7 @@
     <t>Temperature Wire-Open status,BIN,1,0,</t>
   </si>
   <si>
-    <t>Module Temperature Reversion</t>
+    <t>Module Temperature Fault Clear</t>
   </si>
   <si>
     <t>Module Max,I16,0.1,0,℃</t>
@@ -589,7 +586,7 @@
     <t>System AC Power Down</t>
   </si>
   <si>
-    <t>BMU Fault Reversion</t>
+    <t>BMU Fault Clear</t>
   </si>
   <si>
     <t>Reversion BMU ID,U16,1,0,</t>
@@ -602,9 +599,6 @@
   </si>
   <si>
     <t>Precharge Current Limit Value,I16,0.1,0,A</t>
-  </si>
-  <si>
-    <t>String Pole Fault Reversion</t>
   </si>
   <si>
     <t>Reserved</t>
@@ -1777,7 +1771,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{71A443E6-140F-42DB-9935-6391C6A6EDF4}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965B302D-29DC-4994-AFDE-08E93A5B0D3A}">
   <dimension ref="A1:H259"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
@@ -3269,10 +3263,10 @@
         <v>8</v>
       </c>
       <c r="D81" t="s">
+        <v>16</v>
+      </c>
+      <c r="F81" t="s">
         <v>131</v>
-      </c>
-      <c r="F81" t="s">
-        <v>132</v>
       </c>
       <c r="G81" t="s">
         <v>2</v>
@@ -3289,7 +3283,7 @@
         <v>9</v>
       </c>
       <c r="D82" t="s">
-        <v>133</v>
+        <v>132</v>
       </c>
       <c r="E82" t="s">
         <v>19</v>
@@ -3312,7 +3306,7 @@
         <v>10</v>
       </c>
       <c r="D83" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
       <c r="E83" t="s">
         <v>19</v>
@@ -3335,7 +3329,7 @@
         <v>11</v>
       </c>
       <c r="D84" t="s">
-        <v>135</v>
+        <v>134</v>
       </c>
       <c r="E84" t="s">
         <v>24</v>
@@ -3358,7 +3352,7 @@
         <v>12</v>
       </c>
       <c r="D85" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
       <c r="E85" t="s">
         <v>24</v>
@@ -3381,7 +3375,7 @@
         <v>13</v>
       </c>
       <c r="D86" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="87" spans="1:7" x14ac:dyDescent="0.2">
@@ -3395,7 +3389,7 @@
         <v>14</v>
       </c>
       <c r="D87" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="88" spans="1:7" x14ac:dyDescent="0.2">
@@ -3409,7 +3403,7 @@
         <v>15</v>
       </c>
       <c r="D88" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="89" spans="1:7" x14ac:dyDescent="0.2">
@@ -3423,7 +3417,7 @@
         <v>16</v>
       </c>
       <c r="D89" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="90" spans="1:7" x14ac:dyDescent="0.2">
@@ -3440,10 +3434,10 @@
         <v>35</v>
       </c>
       <c r="E90" t="s">
+        <v>140</v>
+      </c>
+      <c r="G90" t="s">
         <v>141</v>
-      </c>
-      <c r="G90" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="91" spans="1:7" x14ac:dyDescent="0.2">
@@ -3457,10 +3451,10 @@
         <v>18</v>
       </c>
       <c r="D91" t="s">
+        <v>142</v>
+      </c>
+      <c r="F91" t="s">
         <v>143</v>
-      </c>
-      <c r="F91" t="s">
-        <v>144</v>
       </c>
       <c r="G91" t="s">
         <v>25</v>
@@ -3526,7 +3520,7 @@
         <v>44</v>
       </c>
       <c r="F94" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G94" t="s">
         <v>21</v>
@@ -3549,7 +3543,7 @@
         <v>48</v>
       </c>
       <c r="G95" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="96" spans="1:7" x14ac:dyDescent="0.2">
@@ -3569,7 +3563,7 @@
         <v>48</v>
       </c>
       <c r="G96" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="97" spans="1:8" x14ac:dyDescent="0.2">
@@ -3589,7 +3583,7 @@
         <v>48</v>
       </c>
       <c r="G97" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="98" spans="1:8" x14ac:dyDescent="0.2">
@@ -3609,7 +3603,7 @@
         <v>48</v>
       </c>
       <c r="G98" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="99" spans="1:8" x14ac:dyDescent="0.2">
@@ -3629,7 +3623,7 @@
         <v>53</v>
       </c>
       <c r="G99" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="100" spans="1:8" x14ac:dyDescent="0.2">
@@ -3649,7 +3643,7 @@
         <v>53</v>
       </c>
       <c r="G100" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="101" spans="1:8" x14ac:dyDescent="0.2">
@@ -3669,7 +3663,7 @@
         <v>53</v>
       </c>
       <c r="G101" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="102" spans="1:8" x14ac:dyDescent="0.2">
@@ -3689,7 +3683,7 @@
         <v>53</v>
       </c>
       <c r="G102" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="103" spans="1:8" x14ac:dyDescent="0.2">
@@ -3709,7 +3703,7 @@
         <v>53</v>
       </c>
       <c r="G103" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="104" spans="1:8" x14ac:dyDescent="0.2">
@@ -3726,10 +3720,10 @@
         <v>58</v>
       </c>
       <c r="F104" t="s">
+        <v>147</v>
+      </c>
+      <c r="G104" t="s">
         <v>148</v>
-      </c>
-      <c r="G104" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="105" spans="1:8" x14ac:dyDescent="0.2">
@@ -3746,10 +3740,10 @@
         <v>60</v>
       </c>
       <c r="F105" t="s">
+        <v>147</v>
+      </c>
+      <c r="G105" t="s">
         <v>148</v>
-      </c>
-      <c r="G105" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="106" spans="1:8" x14ac:dyDescent="0.2">
@@ -3766,10 +3760,10 @@
         <v>61</v>
       </c>
       <c r="F106" t="s">
+        <v>149</v>
+      </c>
+      <c r="G106" t="s">
         <v>150</v>
-      </c>
-      <c r="G106" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="107" spans="1:8" x14ac:dyDescent="0.2">
@@ -3786,10 +3780,10 @@
         <v>63</v>
       </c>
       <c r="F107" t="s">
+        <v>149</v>
+      </c>
+      <c r="G107" t="s">
         <v>150</v>
-      </c>
-      <c r="G107" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="108" spans="1:8" x14ac:dyDescent="0.2">
@@ -3803,19 +3797,19 @@
         <v>35</v>
       </c>
       <c r="D108" t="s">
+        <v>151</v>
+      </c>
+      <c r="E108" t="s">
         <v>152</v>
       </c>
-      <c r="E108" t="s">
+      <c r="F108" t="s">
         <v>153</v>
       </c>
-      <c r="F108" t="s">
+      <c r="G108" t="s">
         <v>154</v>
       </c>
-      <c r="G108" t="s">
+      <c r="H108" t="s">
         <v>155</v>
-      </c>
-      <c r="H108" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="109" spans="1:8" x14ac:dyDescent="0.2">
@@ -3829,16 +3823,16 @@
         <v>36</v>
       </c>
       <c r="D109" t="s">
+        <v>156</v>
+      </c>
+      <c r="E109" t="s">
+        <v>152</v>
+      </c>
+      <c r="F109" t="s">
+        <v>153</v>
+      </c>
+      <c r="H109" t="s">
         <v>157</v>
-      </c>
-      <c r="E109" t="s">
-        <v>153</v>
-      </c>
-      <c r="F109" t="s">
-        <v>154</v>
-      </c>
-      <c r="H109" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="110" spans="1:8" x14ac:dyDescent="0.2">
@@ -3852,19 +3846,19 @@
         <v>37</v>
       </c>
       <c r="D110" t="s">
+        <v>158</v>
+      </c>
+      <c r="E110" t="s">
+        <v>152</v>
+      </c>
+      <c r="F110" t="s">
+        <v>153</v>
+      </c>
+      <c r="G110" t="s">
+        <v>154</v>
+      </c>
+      <c r="H110" t="s">
         <v>159</v>
-      </c>
-      <c r="E110" t="s">
-        <v>153</v>
-      </c>
-      <c r="F110" t="s">
-        <v>154</v>
-      </c>
-      <c r="G110" t="s">
-        <v>155</v>
-      </c>
-      <c r="H110" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="111" spans="1:8" x14ac:dyDescent="0.2">
@@ -3878,16 +3872,16 @@
         <v>38</v>
       </c>
       <c r="D111" t="s">
+        <v>160</v>
+      </c>
+      <c r="E111" t="s">
+        <v>152</v>
+      </c>
+      <c r="F111" t="s">
+        <v>153</v>
+      </c>
+      <c r="H111" t="s">
         <v>161</v>
-      </c>
-      <c r="E111" t="s">
-        <v>153</v>
-      </c>
-      <c r="F111" t="s">
-        <v>154</v>
-      </c>
-      <c r="H111" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="112" spans="1:8" x14ac:dyDescent="0.2">
@@ -3910,7 +3904,7 @@
         <v>53</v>
       </c>
       <c r="G112" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="113" spans="1:8" x14ac:dyDescent="0.2">
@@ -3933,7 +3927,7 @@
         <v>53</v>
       </c>
       <c r="G113" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="114" spans="1:8" x14ac:dyDescent="0.2">
@@ -3947,7 +3941,7 @@
         <v>41</v>
       </c>
       <c r="D114" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="115" spans="1:8" x14ac:dyDescent="0.2">
@@ -3961,7 +3955,7 @@
         <v>42</v>
       </c>
       <c r="D115" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="116" spans="1:8" x14ac:dyDescent="0.2">
@@ -3981,10 +3975,10 @@
         <v>119</v>
       </c>
       <c r="G116" t="s">
+        <v>166</v>
+      </c>
+      <c r="H116" t="s">
         <v>167</v>
-      </c>
-      <c r="H116" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="117" spans="1:8" x14ac:dyDescent="0.2">
@@ -4004,10 +3998,10 @@
         <v>119</v>
       </c>
       <c r="G117" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H117" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="118" spans="1:8" x14ac:dyDescent="0.2">
@@ -4027,10 +4021,10 @@
         <v>119</v>
       </c>
       <c r="G118" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H118" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="119" spans="1:8" x14ac:dyDescent="0.2">
@@ -4050,10 +4044,10 @@
         <v>119</v>
       </c>
       <c r="G119" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H119" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="120" spans="1:8" x14ac:dyDescent="0.2">
@@ -4073,10 +4067,10 @@
         <v>119</v>
       </c>
       <c r="G120" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H120" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="121" spans="1:8" x14ac:dyDescent="0.2">
@@ -4093,13 +4087,13 @@
         <v>84</v>
       </c>
       <c r="E121" t="s">
+        <v>170</v>
+      </c>
+      <c r="F121" t="s">
         <v>171</v>
       </c>
-      <c r="F121" t="s">
+      <c r="G121" t="s">
         <v>172</v>
-      </c>
-      <c r="G121" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="122" spans="1:8" x14ac:dyDescent="0.2">
@@ -4116,13 +4110,13 @@
         <v>86</v>
       </c>
       <c r="E122" t="s">
+        <v>170</v>
+      </c>
+      <c r="F122" t="s">
         <v>171</v>
       </c>
-      <c r="F122" t="s">
+      <c r="G122" t="s">
         <v>172</v>
-      </c>
-      <c r="G122" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="123" spans="1:8" x14ac:dyDescent="0.2">
@@ -4136,10 +4130,10 @@
         <v>50</v>
       </c>
       <c r="D123" t="s">
+        <v>173</v>
+      </c>
+      <c r="E123" t="s">
         <v>174</v>
-      </c>
-      <c r="E123" t="s">
-        <v>175</v>
       </c>
     </row>
     <row r="124" spans="1:8" x14ac:dyDescent="0.2">
@@ -4156,16 +4150,16 @@
         <v>88</v>
       </c>
       <c r="E124" t="s">
+        <v>175</v>
+      </c>
+      <c r="F124" t="s">
         <v>176</v>
       </c>
-      <c r="F124" t="s">
+      <c r="G124" t="s">
         <v>177</v>
       </c>
-      <c r="G124" t="s">
+      <c r="H124" t="s">
         <v>178</v>
-      </c>
-      <c r="H124" t="s">
-        <v>179</v>
       </c>
     </row>
     <row r="125" spans="1:8" x14ac:dyDescent="0.2">
@@ -4221,13 +4215,13 @@
         <v>55</v>
       </c>
       <c r="D128" t="s">
+        <v>179</v>
+      </c>
+      <c r="E128" t="s">
         <v>180</v>
       </c>
-      <c r="E128" t="s">
+      <c r="G128" t="s">
         <v>181</v>
-      </c>
-      <c r="G128" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="129" spans="1:8" x14ac:dyDescent="0.2">
@@ -4241,19 +4235,19 @@
         <v>56</v>
       </c>
       <c r="D129" t="s">
+        <v>182</v>
+      </c>
+      <c r="E129" t="s">
         <v>183</v>
       </c>
-      <c r="E129" t="s">
+      <c r="F129" t="s">
         <v>184</v>
       </c>
-      <c r="F129" t="s">
+      <c r="G129" t="s">
+        <v>183</v>
+      </c>
+      <c r="H129" t="s">
         <v>185</v>
-      </c>
-      <c r="G129" t="s">
-        <v>184</v>
-      </c>
-      <c r="H129" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="130" spans="1:8" x14ac:dyDescent="0.2">
@@ -4267,7 +4261,7 @@
         <v>57</v>
       </c>
       <c r="D130" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="131" spans="1:8" x14ac:dyDescent="0.2">
@@ -4281,7 +4275,7 @@
         <v>58</v>
       </c>
       <c r="D131" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="132" spans="1:8" x14ac:dyDescent="0.2">
@@ -4295,10 +4289,10 @@
         <v>59</v>
       </c>
       <c r="D132" t="s">
+        <v>188</v>
+      </c>
+      <c r="E132" t="s">
         <v>189</v>
-      </c>
-      <c r="E132" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="133" spans="1:8" x14ac:dyDescent="0.2">
@@ -4312,13 +4306,13 @@
         <v>60</v>
       </c>
       <c r="D133" t="s">
+        <v>190</v>
+      </c>
+      <c r="F133" t="s">
         <v>191</v>
       </c>
-      <c r="F133" t="s">
+      <c r="G133" t="s">
         <v>192</v>
-      </c>
-      <c r="G133" t="s">
-        <v>193</v>
       </c>
     </row>
     <row r="134" spans="1:8" x14ac:dyDescent="0.2">
@@ -4335,7 +4329,7 @@
         <v>105</v>
       </c>
       <c r="E134" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="135" spans="1:8" x14ac:dyDescent="0.2">
@@ -4352,7 +4346,7 @@
         <v>106</v>
       </c>
       <c r="E135" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="136" spans="1:8" x14ac:dyDescent="0.2">
@@ -4415,7 +4409,7 @@
         <v>110</v>
       </c>
       <c r="G138" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="139" spans="1:8" x14ac:dyDescent="0.2">
@@ -4429,7 +4423,7 @@
         <v>66</v>
       </c>
       <c r="D139" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="F139" t="s">
         <v>42</v>
@@ -4449,7 +4443,7 @@
         <v>67</v>
       </c>
       <c r="D140" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -4466,10 +4460,10 @@
         <v>116</v>
       </c>
       <c r="E141" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G141" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -4483,16 +4477,16 @@
         <v>69</v>
       </c>
       <c r="D142" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="E142" t="s">
         <v>119</v>
       </c>
       <c r="G142" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H142" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="143" spans="1:8" x14ac:dyDescent="0.2">
@@ -4506,16 +4500,16 @@
         <v>70</v>
       </c>
       <c r="D143" t="s">
+        <v>198</v>
+      </c>
+      <c r="E143" t="s">
+        <v>199</v>
+      </c>
+      <c r="F143" t="s">
+        <v>163</v>
+      </c>
+      <c r="G143" t="s">
         <v>200</v>
-      </c>
-      <c r="E143" t="s">
-        <v>201</v>
-      </c>
-      <c r="F143" t="s">
-        <v>164</v>
-      </c>
-      <c r="G143" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -4529,16 +4523,16 @@
         <v>71</v>
       </c>
       <c r="D144" t="s">
+        <v>201</v>
+      </c>
+      <c r="E144" t="s">
+        <v>202</v>
+      </c>
+      <c r="G144" t="s">
         <v>203</v>
       </c>
-      <c r="E144" t="s">
+      <c r="H144" t="s">
         <v>204</v>
-      </c>
-      <c r="G144" t="s">
-        <v>205</v>
-      </c>
-      <c r="H144" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4552,16 +4546,16 @@
         <v>72</v>
       </c>
       <c r="D145" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E145" t="s">
+        <v>202</v>
+      </c>
+      <c r="G145" t="s">
+        <v>203</v>
+      </c>
+      <c r="H145" t="s">
         <v>204</v>
-      </c>
-      <c r="G145" t="s">
-        <v>205</v>
-      </c>
-      <c r="H145" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -4575,16 +4569,16 @@
         <v>73</v>
       </c>
       <c r="D146" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E146" t="s">
+        <v>202</v>
+      </c>
+      <c r="G146" t="s">
+        <v>203</v>
+      </c>
+      <c r="H146" t="s">
         <v>204</v>
-      </c>
-      <c r="G146" t="s">
-        <v>205</v>
-      </c>
-      <c r="H146" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -4598,16 +4592,16 @@
         <v>74</v>
       </c>
       <c r="D147" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E147" t="s">
+        <v>202</v>
+      </c>
+      <c r="G147" t="s">
+        <v>203</v>
+      </c>
+      <c r="H147" t="s">
         <v>204</v>
-      </c>
-      <c r="G147" t="s">
-        <v>205</v>
-      </c>
-      <c r="H147" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -4624,7 +4618,7 @@
         <v>121</v>
       </c>
       <c r="G148" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -4641,7 +4635,7 @@
         <v>123</v>
       </c>
       <c r="G149" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -4658,7 +4652,7 @@
         <v>124</v>
       </c>
       <c r="G150" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -4675,7 +4669,7 @@
         <v>125</v>
       </c>
       <c r="G151" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -4689,16 +4683,16 @@
         <v>75</v>
       </c>
       <c r="D152" t="s">
+        <v>209</v>
+      </c>
+      <c r="E152" t="s">
+        <v>210</v>
+      </c>
+      <c r="F152" t="s">
         <v>211</v>
       </c>
-      <c r="E152" t="s">
-        <v>212</v>
-      </c>
-      <c r="F152" t="s">
-        <v>213</v>
-      </c>
       <c r="G152" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -4712,7 +4706,7 @@
         <v>76</v>
       </c>
       <c r="D153" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -4726,7 +4720,7 @@
         <v>77</v>
       </c>
       <c r="D154" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4740,13 +4734,13 @@
         <v>78</v>
       </c>
       <c r="D155" t="s">
+        <v>214</v>
+      </c>
+      <c r="F155" t="s">
+        <v>215</v>
+      </c>
+      <c r="G155" t="s">
         <v>216</v>
-      </c>
-      <c r="F155" t="s">
-        <v>217</v>
-      </c>
-      <c r="G155" t="s">
-        <v>218</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -4760,10 +4754,10 @@
         <v>79</v>
       </c>
       <c r="D156" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="G156" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
     </row>
     <row r="157" spans="1:8" x14ac:dyDescent="0.2">
@@ -4777,7 +4771,7 @@
         <v>80</v>
       </c>
       <c r="D157" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="158" spans="1:8" x14ac:dyDescent="0.2">
@@ -4791,13 +4785,13 @@
         <v>81</v>
       </c>
       <c r="D158" t="s">
+        <v>220</v>
+      </c>
+      <c r="E158" t="s">
+        <v>221</v>
+      </c>
+      <c r="H158" t="s">
         <v>222</v>
-      </c>
-      <c r="E158" t="s">
-        <v>223</v>
-      </c>
-      <c r="H158" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="159" spans="1:8" x14ac:dyDescent="0.2">
@@ -4811,13 +4805,13 @@
         <v>82</v>
       </c>
       <c r="D159" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E159" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G159" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -4831,16 +4825,16 @@
         <v>83</v>
       </c>
       <c r="D160" t="s">
+        <v>225</v>
+      </c>
+      <c r="E160" t="s">
+        <v>226</v>
+      </c>
+      <c r="F160" t="s">
         <v>227</v>
       </c>
-      <c r="E160" t="s">
+      <c r="G160" t="s">
         <v>228</v>
-      </c>
-      <c r="F160" t="s">
-        <v>229</v>
-      </c>
-      <c r="G160" t="s">
-        <v>230</v>
       </c>
     </row>
     <row r="161" spans="1:8" x14ac:dyDescent="0.2">
@@ -4854,13 +4848,13 @@
         <v>84</v>
       </c>
       <c r="D161" t="s">
+        <v>229</v>
+      </c>
+      <c r="G161" t="s">
+        <v>230</v>
+      </c>
+      <c r="H161" t="s">
         <v>231</v>
-      </c>
-      <c r="G161" t="s">
-        <v>232</v>
-      </c>
-      <c r="H161" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="162" spans="1:8" x14ac:dyDescent="0.2">
@@ -4874,13 +4868,13 @@
         <v>85</v>
       </c>
       <c r="D162" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F162" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="H162" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
     </row>
     <row r="163" spans="1:8" x14ac:dyDescent="0.2">
@@ -4894,10 +4888,10 @@
         <v>86</v>
       </c>
       <c r="D163" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G163" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="164" spans="1:8" x14ac:dyDescent="0.2">
@@ -4911,13 +4905,13 @@
         <v>87</v>
       </c>
       <c r="D164" t="s">
+        <v>235</v>
+      </c>
+      <c r="F164" t="s">
+        <v>236</v>
+      </c>
+      <c r="G164" t="s">
         <v>237</v>
-      </c>
-      <c r="F164" t="s">
-        <v>238</v>
-      </c>
-      <c r="G164" t="s">
-        <v>239</v>
       </c>
     </row>
     <row r="165" spans="1:8" x14ac:dyDescent="0.2">
@@ -4931,13 +4925,13 @@
         <v>88</v>
       </c>
       <c r="D165" t="s">
+        <v>238</v>
+      </c>
+      <c r="E165" t="s">
+        <v>239</v>
+      </c>
+      <c r="F165" t="s">
         <v>240</v>
-      </c>
-      <c r="E165" t="s">
-        <v>241</v>
-      </c>
-      <c r="F165" t="s">
-        <v>242</v>
       </c>
     </row>
     <row r="166" spans="1:8" x14ac:dyDescent="0.2">
@@ -4951,13 +4945,13 @@
         <v>89</v>
       </c>
       <c r="D166" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
       <c r="E166" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
       <c r="F166" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="167" spans="1:8" x14ac:dyDescent="0.2">
@@ -5063,7 +5057,7 @@
         <v>5</v>
       </c>
       <c r="D171" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="172" spans="1:8" x14ac:dyDescent="0.2">
@@ -5077,7 +5071,7 @@
         <v>6</v>
       </c>
       <c r="D172" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="173" spans="1:8" x14ac:dyDescent="0.2">
@@ -5114,7 +5108,7 @@
         <v>16</v>
       </c>
       <c r="F174" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
       <c r="G174" t="s">
         <v>2</v>
@@ -5223,7 +5217,7 @@
         <v>13</v>
       </c>
       <c r="D179" t="s">
-        <v>137</v>
+        <v>136</v>
       </c>
     </row>
     <row r="180" spans="1:7" x14ac:dyDescent="0.2">
@@ -5237,7 +5231,7 @@
         <v>14</v>
       </c>
       <c r="D180" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="181" spans="1:7" x14ac:dyDescent="0.2">
@@ -5251,7 +5245,7 @@
         <v>15</v>
       </c>
       <c r="D181" t="s">
-        <v>139</v>
+        <v>138</v>
       </c>
     </row>
     <row r="182" spans="1:7" x14ac:dyDescent="0.2">
@@ -5265,7 +5259,7 @@
         <v>16</v>
       </c>
       <c r="D182" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="183" spans="1:7" x14ac:dyDescent="0.2">
@@ -5282,10 +5276,10 @@
         <v>35</v>
       </c>
       <c r="E183" t="s">
+        <v>140</v>
+      </c>
+      <c r="G183" t="s">
         <v>141</v>
-      </c>
-      <c r="G183" t="s">
-        <v>142</v>
       </c>
     </row>
     <row r="184" spans="1:7" x14ac:dyDescent="0.2">
@@ -5299,10 +5293,10 @@
         <v>18</v>
       </c>
       <c r="D184" t="s">
+        <v>142</v>
+      </c>
+      <c r="F184" t="s">
         <v>143</v>
-      </c>
-      <c r="F184" t="s">
-        <v>144</v>
       </c>
       <c r="G184" t="s">
         <v>25</v>
@@ -5368,7 +5362,7 @@
         <v>44</v>
       </c>
       <c r="F187" t="s">
-        <v>145</v>
+        <v>144</v>
       </c>
       <c r="G187" t="s">
         <v>21</v>
@@ -5391,7 +5385,7 @@
         <v>48</v>
       </c>
       <c r="G188" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="189" spans="1:7" x14ac:dyDescent="0.2">
@@ -5411,7 +5405,7 @@
         <v>48</v>
       </c>
       <c r="G189" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="190" spans="1:7" x14ac:dyDescent="0.2">
@@ -5431,7 +5425,7 @@
         <v>48</v>
       </c>
       <c r="G190" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="191" spans="1:7" x14ac:dyDescent="0.2">
@@ -5451,7 +5445,7 @@
         <v>48</v>
       </c>
       <c r="G191" t="s">
-        <v>146</v>
+        <v>145</v>
       </c>
     </row>
     <row r="192" spans="1:7" x14ac:dyDescent="0.2">
@@ -5471,7 +5465,7 @@
         <v>53</v>
       </c>
       <c r="G192" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="193" spans="1:8" x14ac:dyDescent="0.2">
@@ -5491,7 +5485,7 @@
         <v>53</v>
       </c>
       <c r="G193" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="194" spans="1:8" x14ac:dyDescent="0.2">
@@ -5511,7 +5505,7 @@
         <v>53</v>
       </c>
       <c r="G194" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="195" spans="1:8" x14ac:dyDescent="0.2">
@@ -5531,7 +5525,7 @@
         <v>53</v>
       </c>
       <c r="G195" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="196" spans="1:8" x14ac:dyDescent="0.2">
@@ -5551,7 +5545,7 @@
         <v>53</v>
       </c>
       <c r="G196" t="s">
-        <v>147</v>
+        <v>146</v>
       </c>
     </row>
     <row r="197" spans="1:8" x14ac:dyDescent="0.2">
@@ -5568,10 +5562,10 @@
         <v>58</v>
       </c>
       <c r="F197" t="s">
+        <v>147</v>
+      </c>
+      <c r="G197" t="s">
         <v>148</v>
-      </c>
-      <c r="G197" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="198" spans="1:8" x14ac:dyDescent="0.2">
@@ -5588,10 +5582,10 @@
         <v>60</v>
       </c>
       <c r="F198" t="s">
+        <v>147</v>
+      </c>
+      <c r="G198" t="s">
         <v>148</v>
-      </c>
-      <c r="G198" t="s">
-        <v>149</v>
       </c>
     </row>
     <row r="199" spans="1:8" x14ac:dyDescent="0.2">
@@ -5608,10 +5602,10 @@
         <v>61</v>
       </c>
       <c r="F199" t="s">
+        <v>149</v>
+      </c>
+      <c r="G199" t="s">
         <v>150</v>
-      </c>
-      <c r="G199" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="200" spans="1:8" x14ac:dyDescent="0.2">
@@ -5628,10 +5622,10 @@
         <v>63</v>
       </c>
       <c r="F200" t="s">
+        <v>149</v>
+      </c>
+      <c r="G200" t="s">
         <v>150</v>
-      </c>
-      <c r="G200" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="201" spans="1:8" x14ac:dyDescent="0.2">
@@ -5645,19 +5639,19 @@
         <v>35</v>
       </c>
       <c r="D201" t="s">
+        <v>151</v>
+      </c>
+      <c r="E201" t="s">
         <v>152</v>
       </c>
-      <c r="E201" t="s">
+      <c r="F201" t="s">
         <v>153</v>
       </c>
-      <c r="F201" t="s">
+      <c r="G201" t="s">
         <v>154</v>
       </c>
-      <c r="G201" t="s">
+      <c r="H201" t="s">
         <v>155</v>
-      </c>
-      <c r="H201" t="s">
-        <v>156</v>
       </c>
     </row>
     <row r="202" spans="1:8" x14ac:dyDescent="0.2">
@@ -5671,16 +5665,16 @@
         <v>36</v>
       </c>
       <c r="D202" t="s">
+        <v>156</v>
+      </c>
+      <c r="E202" t="s">
+        <v>152</v>
+      </c>
+      <c r="F202" t="s">
+        <v>153</v>
+      </c>
+      <c r="H202" t="s">
         <v>157</v>
-      </c>
-      <c r="E202" t="s">
-        <v>153</v>
-      </c>
-      <c r="F202" t="s">
-        <v>154</v>
-      </c>
-      <c r="H202" t="s">
-        <v>158</v>
       </c>
     </row>
     <row r="203" spans="1:8" x14ac:dyDescent="0.2">
@@ -5694,19 +5688,19 @@
         <v>37</v>
       </c>
       <c r="D203" t="s">
+        <v>158</v>
+      </c>
+      <c r="E203" t="s">
+        <v>152</v>
+      </c>
+      <c r="F203" t="s">
+        <v>153</v>
+      </c>
+      <c r="G203" t="s">
+        <v>154</v>
+      </c>
+      <c r="H203" t="s">
         <v>159</v>
-      </c>
-      <c r="E203" t="s">
-        <v>153</v>
-      </c>
-      <c r="F203" t="s">
-        <v>154</v>
-      </c>
-      <c r="G203" t="s">
-        <v>155</v>
-      </c>
-      <c r="H203" t="s">
-        <v>160</v>
       </c>
     </row>
     <row r="204" spans="1:8" x14ac:dyDescent="0.2">
@@ -5720,16 +5714,16 @@
         <v>38</v>
       </c>
       <c r="D204" t="s">
+        <v>160</v>
+      </c>
+      <c r="E204" t="s">
+        <v>152</v>
+      </c>
+      <c r="F204" t="s">
+        <v>153</v>
+      </c>
+      <c r="H204" t="s">
         <v>161</v>
-      </c>
-      <c r="E204" t="s">
-        <v>153</v>
-      </c>
-      <c r="F204" t="s">
-        <v>154</v>
-      </c>
-      <c r="H204" t="s">
-        <v>162</v>
       </c>
     </row>
     <row r="205" spans="1:8" x14ac:dyDescent="0.2">
@@ -5752,7 +5746,7 @@
         <v>53</v>
       </c>
       <c r="G205" t="s">
-        <v>163</v>
+        <v>162</v>
       </c>
     </row>
     <row r="206" spans="1:8" x14ac:dyDescent="0.2">
@@ -5775,7 +5769,7 @@
         <v>53</v>
       </c>
       <c r="G206" t="s">
-        <v>164</v>
+        <v>163</v>
       </c>
     </row>
     <row r="207" spans="1:8" x14ac:dyDescent="0.2">
@@ -5789,7 +5783,7 @@
         <v>41</v>
       </c>
       <c r="D207" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="208" spans="1:8" x14ac:dyDescent="0.2">
@@ -5803,7 +5797,7 @@
         <v>42</v>
       </c>
       <c r="D208" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
     </row>
     <row r="209" spans="1:8" x14ac:dyDescent="0.2">
@@ -5823,10 +5817,10 @@
         <v>119</v>
       </c>
       <c r="G209" t="s">
+        <v>166</v>
+      </c>
+      <c r="H209" t="s">
         <v>167</v>
-      </c>
-      <c r="H209" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="210" spans="1:8" x14ac:dyDescent="0.2">
@@ -5846,10 +5840,10 @@
         <v>119</v>
       </c>
       <c r="G210" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H210" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="211" spans="1:8" x14ac:dyDescent="0.2">
@@ -5869,10 +5863,10 @@
         <v>119</v>
       </c>
       <c r="G211" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H211" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="212" spans="1:8" x14ac:dyDescent="0.2">
@@ -5892,10 +5886,10 @@
         <v>119</v>
       </c>
       <c r="G212" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
       <c r="H212" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="213" spans="1:8" x14ac:dyDescent="0.2">
@@ -5915,10 +5909,10 @@
         <v>119</v>
       </c>
       <c r="G213" t="s">
-        <v>170</v>
+        <v>169</v>
       </c>
       <c r="H213" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="214" spans="1:8" x14ac:dyDescent="0.2">
@@ -5935,13 +5929,13 @@
         <v>84</v>
       </c>
       <c r="E214" t="s">
+        <v>170</v>
+      </c>
+      <c r="F214" t="s">
         <v>171</v>
       </c>
-      <c r="F214" t="s">
+      <c r="G214" t="s">
         <v>172</v>
-      </c>
-      <c r="G214" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="215" spans="1:8" x14ac:dyDescent="0.2">
@@ -5958,13 +5952,13 @@
         <v>86</v>
       </c>
       <c r="E215" t="s">
+        <v>170</v>
+      </c>
+      <c r="F215" t="s">
         <v>171</v>
       </c>
-      <c r="F215" t="s">
+      <c r="G215" t="s">
         <v>172</v>
-      </c>
-      <c r="G215" t="s">
-        <v>173</v>
       </c>
     </row>
     <row r="216" spans="1:8" x14ac:dyDescent="0.2">
@@ -5978,10 +5972,10 @@
         <v>50</v>
       </c>
       <c r="D216" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E216" t="s">
-        <v>175</v>
+        <v>174</v>
       </c>
     </row>
     <row r="217" spans="1:8" x14ac:dyDescent="0.2">
@@ -5998,16 +5992,16 @@
         <v>88</v>
       </c>
       <c r="E217" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="F217" t="s">
+        <v>176</v>
+      </c>
+      <c r="G217" t="s">
         <v>177</v>
       </c>
-      <c r="G217" t="s">
-        <v>178</v>
-      </c>
       <c r="H217" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
     </row>
     <row r="218" spans="1:8" x14ac:dyDescent="0.2">
@@ -6021,7 +6015,7 @@
         <v>52</v>
       </c>
       <c r="D218" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
     </row>
     <row r="219" spans="1:8" x14ac:dyDescent="0.2">
@@ -6035,7 +6029,7 @@
         <v>53</v>
       </c>
       <c r="D219" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
     </row>
     <row r="220" spans="1:8" x14ac:dyDescent="0.2">
@@ -6049,7 +6043,7 @@
         <v>54</v>
       </c>
       <c r="D220" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
     </row>
     <row r="221" spans="1:8" x14ac:dyDescent="0.2">
@@ -6063,13 +6057,13 @@
         <v>55</v>
       </c>
       <c r="D221" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E221" t="s">
+        <v>180</v>
+      </c>
+      <c r="G221" t="s">
         <v>181</v>
-      </c>
-      <c r="G221" t="s">
-        <v>182</v>
       </c>
     </row>
     <row r="222" spans="1:8" x14ac:dyDescent="0.2">
@@ -6083,19 +6077,19 @@
         <v>56</v>
       </c>
       <c r="D222" t="s">
+        <v>182</v>
+      </c>
+      <c r="E222" t="s">
         <v>183</v>
       </c>
-      <c r="E222" t="s">
+      <c r="F222" t="s">
         <v>184</v>
       </c>
-      <c r="F222" t="s">
+      <c r="G222" t="s">
+        <v>183</v>
+      </c>
+      <c r="H222" t="s">
         <v>185</v>
-      </c>
-      <c r="G222" t="s">
-        <v>184</v>
-      </c>
-      <c r="H222" t="s">
-        <v>186</v>
       </c>
     </row>
     <row r="223" spans="1:8" x14ac:dyDescent="0.2">
@@ -6109,7 +6103,7 @@
         <v>57</v>
       </c>
       <c r="D223" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="224" spans="1:8" x14ac:dyDescent="0.2">
@@ -6123,7 +6117,7 @@
         <v>58</v>
       </c>
       <c r="D224" t="s">
-        <v>188</v>
+        <v>187</v>
       </c>
     </row>
     <row r="225" spans="1:8" x14ac:dyDescent="0.2">
@@ -6137,10 +6131,10 @@
         <v>59</v>
       </c>
       <c r="D225" t="s">
+        <v>188</v>
+      </c>
+      <c r="E225" t="s">
         <v>189</v>
-      </c>
-      <c r="E225" t="s">
-        <v>190</v>
       </c>
     </row>
     <row r="226" spans="1:8" x14ac:dyDescent="0.2">
@@ -6154,13 +6148,13 @@
         <v>60</v>
       </c>
       <c r="D226" t="s">
-        <v>191</v>
+        <v>190</v>
       </c>
       <c r="F226" t="s">
         <v>48</v>
       </c>
       <c r="G226" t="s">
-        <v>193</v>
+        <v>192</v>
       </c>
     </row>
     <row r="227" spans="1:8" x14ac:dyDescent="0.2">
@@ -6177,7 +6171,7 @@
         <v>105</v>
       </c>
       <c r="E227" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="228" spans="1:8" x14ac:dyDescent="0.2">
@@ -6194,7 +6188,7 @@
         <v>106</v>
       </c>
       <c r="E228" t="s">
-        <v>190</v>
+        <v>189</v>
       </c>
     </row>
     <row r="229" spans="1:8" x14ac:dyDescent="0.2">
@@ -6257,7 +6251,7 @@
         <v>110</v>
       </c>
       <c r="G231" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
     </row>
     <row r="232" spans="1:8" x14ac:dyDescent="0.2">
@@ -6271,7 +6265,7 @@
         <v>66</v>
       </c>
       <c r="D232" t="s">
-        <v>194</v>
+        <v>112</v>
       </c>
       <c r="F232" t="s">
         <v>42</v>
@@ -6291,7 +6285,7 @@
         <v>67</v>
       </c>
       <c r="D233" t="s">
-        <v>195</v>
+        <v>193</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -6305,13 +6299,13 @@
         <v>68</v>
       </c>
       <c r="D234" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="E234" t="s">
-        <v>196</v>
+        <v>194</v>
       </c>
       <c r="G234" t="s">
-        <v>197</v>
+        <v>195</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -6325,16 +6319,16 @@
         <v>69</v>
       </c>
       <c r="D235" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="E235" t="s">
         <v>119</v>
       </c>
       <c r="G235" t="s">
-        <v>199</v>
+        <v>197</v>
       </c>
       <c r="H235" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
     </row>
     <row r="236" spans="1:8" x14ac:dyDescent="0.2">
@@ -6348,16 +6342,16 @@
         <v>70</v>
       </c>
       <c r="D236" t="s">
+        <v>198</v>
+      </c>
+      <c r="E236" t="s">
+        <v>199</v>
+      </c>
+      <c r="F236" t="s">
+        <v>163</v>
+      </c>
+      <c r="G236" t="s">
         <v>200</v>
-      </c>
-      <c r="E236" t="s">
-        <v>201</v>
-      </c>
-      <c r="F236" t="s">
-        <v>164</v>
-      </c>
-      <c r="G236" t="s">
-        <v>202</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -6371,16 +6365,16 @@
         <v>71</v>
       </c>
       <c r="D237" t="s">
+        <v>201</v>
+      </c>
+      <c r="E237" t="s">
+        <v>202</v>
+      </c>
+      <c r="G237" t="s">
         <v>203</v>
       </c>
-      <c r="E237" t="s">
+      <c r="H237" t="s">
         <v>204</v>
-      </c>
-      <c r="G237" t="s">
-        <v>205</v>
-      </c>
-      <c r="H237" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -6394,16 +6388,16 @@
         <v>72</v>
       </c>
       <c r="D238" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="E238" t="s">
+        <v>202</v>
+      </c>
+      <c r="G238" t="s">
+        <v>203</v>
+      </c>
+      <c r="H238" t="s">
         <v>204</v>
-      </c>
-      <c r="G238" t="s">
-        <v>205</v>
-      </c>
-      <c r="H238" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -6417,16 +6411,16 @@
         <v>73</v>
       </c>
       <c r="D239" t="s">
-        <v>208</v>
+        <v>206</v>
       </c>
       <c r="E239" t="s">
+        <v>202</v>
+      </c>
+      <c r="G239" t="s">
+        <v>203</v>
+      </c>
+      <c r="H239" t="s">
         <v>204</v>
-      </c>
-      <c r="G239" t="s">
-        <v>205</v>
-      </c>
-      <c r="H239" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -6440,16 +6434,16 @@
         <v>74</v>
       </c>
       <c r="D240" t="s">
-        <v>209</v>
+        <v>207</v>
       </c>
       <c r="E240" t="s">
+        <v>202</v>
+      </c>
+      <c r="G240" t="s">
+        <v>203</v>
+      </c>
+      <c r="H240" t="s">
         <v>204</v>
-      </c>
-      <c r="G240" t="s">
-        <v>205</v>
-      </c>
-      <c r="H240" t="s">
-        <v>206</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -6466,7 +6460,7 @@
         <v>121</v>
       </c>
       <c r="G241" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
@@ -6483,7 +6477,7 @@
         <v>123</v>
       </c>
       <c r="G242" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -6500,7 +6494,7 @@
         <v>124</v>
       </c>
       <c r="G243" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -6517,7 +6511,7 @@
         <v>125</v>
       </c>
       <c r="G244" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
@@ -6531,16 +6525,16 @@
         <v>75</v>
       </c>
       <c r="D245" t="s">
+        <v>209</v>
+      </c>
+      <c r="E245" t="s">
+        <v>253</v>
+      </c>
+      <c r="F245" t="s">
         <v>211</v>
       </c>
-      <c r="E245" t="s">
-        <v>255</v>
-      </c>
-      <c r="F245" t="s">
-        <v>213</v>
-      </c>
       <c r="G245" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -6554,7 +6548,7 @@
         <v>76</v>
       </c>
       <c r="D246" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -6568,7 +6562,7 @@
         <v>77</v>
       </c>
       <c r="D247" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -6582,13 +6576,13 @@
         <v>78</v>
       </c>
       <c r="D248" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F248" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
       <c r="G248" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="249" spans="1:8" x14ac:dyDescent="0.2">
@@ -6602,13 +6596,13 @@
         <v>79</v>
       </c>
       <c r="D249" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="F249" t="s">
-        <v>220</v>
+        <v>218</v>
       </c>
       <c r="G249" t="s">
-        <v>259</v>
+        <v>257</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -6622,7 +6616,7 @@
         <v>80</v>
       </c>
       <c r="D250" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="251" spans="1:8" x14ac:dyDescent="0.2">
@@ -6636,13 +6630,13 @@
         <v>81</v>
       </c>
       <c r="D251" t="s">
+        <v>220</v>
+      </c>
+      <c r="E251" t="s">
+        <v>221</v>
+      </c>
+      <c r="H251" t="s">
         <v>222</v>
-      </c>
-      <c r="E251" t="s">
-        <v>223</v>
-      </c>
-      <c r="H251" t="s">
-        <v>224</v>
       </c>
     </row>
     <row r="252" spans="1:8" x14ac:dyDescent="0.2">
@@ -6656,13 +6650,13 @@
         <v>82</v>
       </c>
       <c r="D252" t="s">
-        <v>225</v>
+        <v>223</v>
       </c>
       <c r="E252" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
       <c r="G252" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -6676,16 +6670,16 @@
         <v>83</v>
       </c>
       <c r="D253" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="E253" t="s">
-        <v>261</v>
+        <v>259</v>
       </c>
       <c r="F253" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="G253" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="254" spans="1:8" x14ac:dyDescent="0.2">
@@ -6699,13 +6693,13 @@
         <v>84</v>
       </c>
       <c r="D254" t="s">
+        <v>229</v>
+      </c>
+      <c r="G254" t="s">
+        <v>230</v>
+      </c>
+      <c r="H254" t="s">
         <v>231</v>
-      </c>
-      <c r="G254" t="s">
-        <v>232</v>
-      </c>
-      <c r="H254" t="s">
-        <v>233</v>
       </c>
     </row>
     <row r="255" spans="1:8" x14ac:dyDescent="0.2">
@@ -6719,10 +6713,10 @@
         <v>85</v>
       </c>
       <c r="D255" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="F255" t="s">
-        <v>262</v>
+        <v>260</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -6736,10 +6730,10 @@
         <v>86</v>
       </c>
       <c r="D256" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="G256" t="s">
-        <v>226</v>
+        <v>224</v>
       </c>
     </row>
     <row r="257" spans="1:7" x14ac:dyDescent="0.2">
@@ -6753,13 +6747,13 @@
         <v>87</v>
       </c>
       <c r="D257" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="F257" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
       <c r="G257" t="s">
-        <v>263</v>
+        <v>261</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -6773,7 +6767,7 @@
         <v>89</v>
       </c>
       <c r="D258" t="s">
-        <v>264</v>
+        <v>262</v>
       </c>
       <c r="E258" t="s">
         <v>6</v>
@@ -6793,16 +6787,16 @@
         <v>90</v>
       </c>
       <c r="D259" t="s">
+        <v>263</v>
+      </c>
+      <c r="E259" t="s">
+        <v>264</v>
+      </c>
+      <c r="F259" t="s">
         <v>265</v>
       </c>
-      <c r="E259" t="s">
+      <c r="G259" t="s">
         <v>266</v>
-      </c>
-      <c r="F259" t="s">
-        <v>267</v>
-      </c>
-      <c r="G259" t="s">
-        <v>268</v>
       </c>
     </row>
   </sheetData>

--- a/doc/en_US.xlsx
+++ b/doc/en_US.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28730"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\QT\workSpace\BMSTOOL\bmsTool\doc\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="8_{97376734-4759-4065-93E5-3F92EC050994}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="8_{50C69AB7-BB45-49FB-BE41-279E70C11DBF}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="1755" yWindow="7335" windowWidth="23250" windowHeight="12810" xr2:uid="{C4F1E5FA-5995-4FB6-94E9-A8F7207975B8}"/>
+    <workbookView xWindow="34800" yWindow="2835" windowWidth="21600" windowHeight="11385" xr2:uid="{B359CD0C-C5DF-438B-A435-476841CCF0BD}"/>
   </bookViews>
   <sheets>
     <sheet name="en_US" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="725" uniqueCount="267">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1078" uniqueCount="299">
   <si>
     <t>Cell UV Alarm</t>
   </si>
@@ -466,7 +466,7 @@
     <t>INS RES,U16,0.1,0,kΩ</t>
   </si>
   <si>
-    <t>INS RES Threshold,U16,0.1,0,kΩ</t>
+    <t>INS RES Threshold,U16,1,0,kΩ</t>
   </si>
   <si>
     <t>leakage Current,I16,0.1,0,mA</t>
@@ -601,9 +601,6 @@
     <t>Precharge Current Limit Value,I16,0.1,0,A</t>
   </si>
   <si>
-    <t>Reserved</t>
-  </si>
-  <si>
     <t>DI status,U16,1,0,</t>
   </si>
   <si>
@@ -673,12 +670,15 @@
     <t>PE-B- Voltage,U16,0.1,0,V</t>
   </si>
   <si>
-    <t>Reserved Current SensorWire-Open</t>
+    <t>Current Sensor Wire-Open</t>
   </si>
   <si>
     <t>Two Current Sensor Difference,U16,1,0,A</t>
   </si>
   <si>
+    <t>{"evt_id":{"0":"Ain Sensor Wire-Open","1":"CAN Sensor Wire-Open"}}</t>
+  </si>
+  <si>
     <t>RTC Read Failed</t>
   </si>
   <si>
@@ -790,9 +790,6 @@
     <t>BUS PE-B- Voltage,U16,0.1,0,V</t>
   </si>
   <si>
-    <t>ReservedCurrent SensorWire-Open</t>
-  </si>
-  <si>
     <t>Current Sensor Difference,U16,1,0,A</t>
   </si>
   <si>
@@ -821,6 +818,105 @@
   </si>
   <si>
     <t>After Jump Temperature,U16,0.1,0,℃</t>
+  </si>
+  <si>
+    <t>String Volt DIff Alarm</t>
+  </si>
+  <si>
+    <t>Voltage DIff,I16,1,0,V</t>
+  </si>
+  <si>
+    <t>Voltage Threshold,U16,1,0,V</t>
+  </si>
+  <si>
+    <t>leakage Current Threshold,I16,1,0,mA</t>
+  </si>
+  <si>
+    <t>OV Automatic Trip</t>
+  </si>
+  <si>
+    <t>ID,U16,1,0,</t>
+  </si>
+  <si>
+    <t>Capacity Verification Accomplished</t>
+  </si>
+  <si>
+    <t>SOH,U16,1,0,‰</t>
+  </si>
+  <si>
+    <t>SOH,U16,1,0,%</t>
+  </si>
+  <si>
+    <t>Cell Voltage Abnormal</t>
+  </si>
+  <si>
+    <t>BMU-ID</t>
+  </si>
+  <si>
+    <t>Cell ID</t>
+  </si>
+  <si>
+    <t>Aerosol Fault</t>
+  </si>
+  <si>
+    <t>Fault Stat Bits,U16,1,0,</t>
+  </si>
+  <si>
+    <t>String Voltage Abnormal</t>
+  </si>
+  <si>
+    <t>Function Enable Stat1 Bits,U16,1,0,</t>
+  </si>
+  <si>
+    <t>CMU-BMU Comm Fault</t>
+  </si>
+  <si>
+    <t>CMU-INR Comm Fault</t>
+  </si>
+  <si>
+    <t>OC Lock</t>
+  </si>
+  <si>
+    <t>OV Lock</t>
+  </si>
+  <si>
+    <t>Module OT Lock</t>
+  </si>
+  <si>
+    <t>Module UT Lock</t>
+  </si>
+  <si>
+    <t>Pole OT Lock</t>
+  </si>
+  <si>
+    <t>String Pole OT Lock</t>
+  </si>
+  <si>
+    <t>Current Sensor Abnormal Clear</t>
+  </si>
+  <si>
+    <t>UV Lock</t>
+  </si>
+  <si>
+    <t>Bus Bar OT Lock</t>
+  </si>
+  <si>
+    <t>Bus Bar UT Lock</t>
+  </si>
+  <si>
+    <t>Bus Bar OT Fault</t>
+  </si>
+  <si>
+    <t>Bus Bar OT Alarm</t>
+  </si>
+  <si>
+    <t>Bus Bar UT Falut</t>
+  </si>
+  <si>
+    <t>Bus Bar UT Alarm</t>
+  </si>
+  <si>
+    <t>Bus Bar Temp Error Clear</t>
   </si>
 </sst>
 </file>
@@ -1771,8 +1867,8 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{965B302D-29DC-4994-AFDE-08E93A5B0D3A}">
-  <dimension ref="A1:H259"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{D02ABCC6-CA0F-4A6B-83E4-B1A54DB8F602}">
+  <dimension ref="A1:H374"/>
   <sheetFormatPr defaultRowHeight="14.25" x14ac:dyDescent="0.2"/>
   <sheetData>
     <row r="1" spans="1:7" x14ac:dyDescent="0.2">
@@ -4443,7 +4539,7 @@
         <v>67</v>
       </c>
       <c r="D140" t="s">
-        <v>193</v>
+        <v>114</v>
       </c>
     </row>
     <row r="141" spans="1:8" x14ac:dyDescent="0.2">
@@ -4460,10 +4556,10 @@
         <v>116</v>
       </c>
       <c r="E141" t="s">
+        <v>193</v>
+      </c>
+      <c r="G141" t="s">
         <v>194</v>
-      </c>
-      <c r="G141" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="142" spans="1:8" x14ac:dyDescent="0.2">
@@ -4477,13 +4573,13 @@
         <v>69</v>
       </c>
       <c r="D142" t="s">
-        <v>196</v>
+        <v>195</v>
       </c>
       <c r="E142" t="s">
         <v>119</v>
       </c>
       <c r="G142" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H142" t="s">
         <v>167</v>
@@ -4500,16 +4596,16 @@
         <v>70</v>
       </c>
       <c r="D143" t="s">
+        <v>197</v>
+      </c>
+      <c r="E143" t="s">
         <v>198</v>
-      </c>
-      <c r="E143" t="s">
-        <v>199</v>
       </c>
       <c r="F143" t="s">
         <v>163</v>
       </c>
       <c r="G143" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="144" spans="1:8" x14ac:dyDescent="0.2">
@@ -4523,16 +4619,16 @@
         <v>71</v>
       </c>
       <c r="D144" t="s">
+        <v>200</v>
+      </c>
+      <c r="E144" t="s">
         <v>201</v>
       </c>
-      <c r="E144" t="s">
+      <c r="G144" t="s">
         <v>202</v>
       </c>
-      <c r="G144" t="s">
+      <c r="H144" t="s">
         <v>203</v>
-      </c>
-      <c r="H144" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="145" spans="1:8" x14ac:dyDescent="0.2">
@@ -4546,16 +4642,16 @@
         <v>72</v>
       </c>
       <c r="D145" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E145" t="s">
+        <v>201</v>
+      </c>
+      <c r="G145" t="s">
         <v>202</v>
       </c>
-      <c r="G145" t="s">
+      <c r="H145" t="s">
         <v>203</v>
-      </c>
-      <c r="H145" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="146" spans="1:8" x14ac:dyDescent="0.2">
@@ -4569,16 +4665,16 @@
         <v>73</v>
       </c>
       <c r="D146" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E146" t="s">
+        <v>201</v>
+      </c>
+      <c r="G146" t="s">
         <v>202</v>
       </c>
-      <c r="G146" t="s">
+      <c r="H146" t="s">
         <v>203</v>
-      </c>
-      <c r="H146" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="147" spans="1:8" x14ac:dyDescent="0.2">
@@ -4592,16 +4688,16 @@
         <v>74</v>
       </c>
       <c r="D147" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E147" t="s">
+        <v>201</v>
+      </c>
+      <c r="G147" t="s">
         <v>202</v>
       </c>
-      <c r="G147" t="s">
+      <c r="H147" t="s">
         <v>203</v>
-      </c>
-      <c r="H147" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="148" spans="1:8" x14ac:dyDescent="0.2">
@@ -4618,7 +4714,7 @@
         <v>121</v>
       </c>
       <c r="G148" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="149" spans="1:8" x14ac:dyDescent="0.2">
@@ -4635,7 +4731,7 @@
         <v>123</v>
       </c>
       <c r="G149" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="150" spans="1:8" x14ac:dyDescent="0.2">
@@ -4652,7 +4748,7 @@
         <v>124</v>
       </c>
       <c r="G150" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="151" spans="1:8" x14ac:dyDescent="0.2">
@@ -4669,7 +4765,7 @@
         <v>125</v>
       </c>
       <c r="G151" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="152" spans="1:8" x14ac:dyDescent="0.2">
@@ -4683,16 +4779,16 @@
         <v>75</v>
       </c>
       <c r="D152" t="s">
+        <v>208</v>
+      </c>
+      <c r="E152" t="s">
         <v>209</v>
       </c>
-      <c r="E152" t="s">
+      <c r="F152" t="s">
         <v>210</v>
       </c>
-      <c r="F152" t="s">
-        <v>211</v>
-      </c>
       <c r="G152" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="153" spans="1:8" x14ac:dyDescent="0.2">
@@ -4706,7 +4802,7 @@
         <v>76</v>
       </c>
       <c r="D153" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="154" spans="1:8" x14ac:dyDescent="0.2">
@@ -4720,7 +4816,7 @@
         <v>77</v>
       </c>
       <c r="D154" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="155" spans="1:8" x14ac:dyDescent="0.2">
@@ -4734,13 +4830,13 @@
         <v>78</v>
       </c>
       <c r="D155" t="s">
+        <v>213</v>
+      </c>
+      <c r="F155" t="s">
         <v>214</v>
       </c>
-      <c r="F155" t="s">
+      <c r="G155" t="s">
         <v>215</v>
-      </c>
-      <c r="G155" t="s">
-        <v>216</v>
       </c>
     </row>
     <row r="156" spans="1:8" x14ac:dyDescent="0.2">
@@ -4754,9 +4850,15 @@
         <v>79</v>
       </c>
       <c r="D156" t="s">
+        <v>216</v>
+      </c>
+      <c r="E156" t="s">
+        <v>183</v>
+      </c>
+      <c r="G156" t="s">
         <v>217</v>
       </c>
-      <c r="G156" t="s">
+      <c r="H156" t="s">
         <v>218</v>
       </c>
     </row>
@@ -4811,7 +4913,7 @@
         <v>224</v>
       </c>
       <c r="G159" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="160" spans="1:8" x14ac:dyDescent="0.2">
@@ -6285,7 +6387,7 @@
         <v>67</v>
       </c>
       <c r="D233" t="s">
-        <v>193</v>
+        <v>114</v>
       </c>
     </row>
     <row r="234" spans="1:8" x14ac:dyDescent="0.2">
@@ -6302,10 +6404,10 @@
         <v>251</v>
       </c>
       <c r="E234" t="s">
+        <v>193</v>
+      </c>
+      <c r="G234" t="s">
         <v>194</v>
-      </c>
-      <c r="G234" t="s">
-        <v>195</v>
       </c>
     </row>
     <row r="235" spans="1:8" x14ac:dyDescent="0.2">
@@ -6325,7 +6427,7 @@
         <v>119</v>
       </c>
       <c r="G235" t="s">
-        <v>197</v>
+        <v>196</v>
       </c>
       <c r="H235" t="s">
         <v>167</v>
@@ -6342,16 +6444,16 @@
         <v>70</v>
       </c>
       <c r="D236" t="s">
+        <v>197</v>
+      </c>
+      <c r="E236" t="s">
         <v>198</v>
-      </c>
-      <c r="E236" t="s">
-        <v>199</v>
       </c>
       <c r="F236" t="s">
         <v>163</v>
       </c>
       <c r="G236" t="s">
-        <v>200</v>
+        <v>199</v>
       </c>
     </row>
     <row r="237" spans="1:8" x14ac:dyDescent="0.2">
@@ -6365,16 +6467,16 @@
         <v>71</v>
       </c>
       <c r="D237" t="s">
+        <v>200</v>
+      </c>
+      <c r="E237" t="s">
         <v>201</v>
       </c>
-      <c r="E237" t="s">
+      <c r="G237" t="s">
         <v>202</v>
       </c>
-      <c r="G237" t="s">
+      <c r="H237" t="s">
         <v>203</v>
-      </c>
-      <c r="H237" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="238" spans="1:8" x14ac:dyDescent="0.2">
@@ -6388,16 +6490,16 @@
         <v>72</v>
       </c>
       <c r="D238" t="s">
-        <v>205</v>
+        <v>204</v>
       </c>
       <c r="E238" t="s">
+        <v>201</v>
+      </c>
+      <c r="G238" t="s">
         <v>202</v>
       </c>
-      <c r="G238" t="s">
+      <c r="H238" t="s">
         <v>203</v>
-      </c>
-      <c r="H238" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="239" spans="1:8" x14ac:dyDescent="0.2">
@@ -6411,16 +6513,16 @@
         <v>73</v>
       </c>
       <c r="D239" t="s">
-        <v>206</v>
+        <v>205</v>
       </c>
       <c r="E239" t="s">
+        <v>201</v>
+      </c>
+      <c r="G239" t="s">
         <v>202</v>
       </c>
-      <c r="G239" t="s">
+      <c r="H239" t="s">
         <v>203</v>
-      </c>
-      <c r="H239" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="240" spans="1:8" x14ac:dyDescent="0.2">
@@ -6434,16 +6536,16 @@
         <v>74</v>
       </c>
       <c r="D240" t="s">
-        <v>207</v>
+        <v>206</v>
       </c>
       <c r="E240" t="s">
+        <v>201</v>
+      </c>
+      <c r="G240" t="s">
         <v>202</v>
       </c>
-      <c r="G240" t="s">
+      <c r="H240" t="s">
         <v>203</v>
-      </c>
-      <c r="H240" t="s">
-        <v>204</v>
       </c>
     </row>
     <row r="241" spans="1:8" x14ac:dyDescent="0.2">
@@ -6460,7 +6562,7 @@
         <v>121</v>
       </c>
       <c r="G241" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="242" spans="1:8" x14ac:dyDescent="0.2">
@@ -6477,7 +6579,7 @@
         <v>123</v>
       </c>
       <c r="G242" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="243" spans="1:8" x14ac:dyDescent="0.2">
@@ -6494,7 +6596,7 @@
         <v>124</v>
       </c>
       <c r="G243" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="244" spans="1:8" x14ac:dyDescent="0.2">
@@ -6511,7 +6613,7 @@
         <v>125</v>
       </c>
       <c r="G244" t="s">
-        <v>208</v>
+        <v>207</v>
       </c>
     </row>
     <row r="245" spans="1:8" x14ac:dyDescent="0.2">
@@ -6525,16 +6627,16 @@
         <v>75</v>
       </c>
       <c r="D245" t="s">
-        <v>209</v>
+        <v>208</v>
       </c>
       <c r="E245" t="s">
         <v>253</v>
       </c>
       <c r="F245" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
       <c r="G245" t="s">
-        <v>211</v>
+        <v>210</v>
       </c>
     </row>
     <row r="246" spans="1:8" x14ac:dyDescent="0.2">
@@ -6548,7 +6650,7 @@
         <v>76</v>
       </c>
       <c r="D246" t="s">
-        <v>212</v>
+        <v>211</v>
       </c>
     </row>
     <row r="247" spans="1:8" x14ac:dyDescent="0.2">
@@ -6562,7 +6664,7 @@
         <v>77</v>
       </c>
       <c r="D247" t="s">
-        <v>213</v>
+        <v>212</v>
       </c>
     </row>
     <row r="248" spans="1:8" x14ac:dyDescent="0.2">
@@ -6576,7 +6678,7 @@
         <v>78</v>
       </c>
       <c r="D248" t="s">
-        <v>214</v>
+        <v>213</v>
       </c>
       <c r="F248" t="s">
         <v>254</v>
@@ -6596,13 +6698,19 @@
         <v>79</v>
       </c>
       <c r="D249" t="s">
+        <v>216</v>
+      </c>
+      <c r="E249" t="s">
+        <v>183</v>
+      </c>
+      <c r="F249" t="s">
+        <v>217</v>
+      </c>
+      <c r="G249" t="s">
         <v>256</v>
       </c>
-      <c r="F249" t="s">
+      <c r="H249" t="s">
         <v>218</v>
-      </c>
-      <c r="G249" t="s">
-        <v>257</v>
       </c>
     </row>
     <row r="250" spans="1:8" x14ac:dyDescent="0.2">
@@ -6656,7 +6764,7 @@
         <v>224</v>
       </c>
       <c r="G252" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
     </row>
     <row r="253" spans="1:8" x14ac:dyDescent="0.2">
@@ -6670,10 +6778,10 @@
         <v>83</v>
       </c>
       <c r="D253" t="s">
+        <v>257</v>
+      </c>
+      <c r="E253" t="s">
         <v>258</v>
-      </c>
-      <c r="E253" t="s">
-        <v>259</v>
       </c>
       <c r="F253" t="s">
         <v>227</v>
@@ -6716,7 +6824,7 @@
         <v>232</v>
       </c>
       <c r="F255" t="s">
-        <v>260</v>
+        <v>259</v>
       </c>
     </row>
     <row r="256" spans="1:8" x14ac:dyDescent="0.2">
@@ -6753,7 +6861,7 @@
         <v>236</v>
       </c>
       <c r="G257" t="s">
-        <v>261</v>
+        <v>260</v>
       </c>
     </row>
     <row r="258" spans="1:7" x14ac:dyDescent="0.2">
@@ -6767,7 +6875,7 @@
         <v>89</v>
       </c>
       <c r="D258" t="s">
-        <v>262</v>
+        <v>261</v>
       </c>
       <c r="E258" t="s">
         <v>6</v>
@@ -6787,16 +6895,2328 @@
         <v>90</v>
       </c>
       <c r="D259" t="s">
+        <v>262</v>
+      </c>
+      <c r="E259" t="s">
         <v>263</v>
       </c>
-      <c r="E259" t="s">
+      <c r="F259" t="s">
         <v>264</v>
       </c>
-      <c r="F259" t="s">
+      <c r="G259" t="s">
         <v>265</v>
       </c>
-      <c r="G259" t="s">
+    </row>
+    <row r="260" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A260">
+        <v>260</v>
+      </c>
+      <c r="B260">
+        <v>4</v>
+      </c>
+      <c r="C260">
+        <v>1</v>
+      </c>
+      <c r="D260" t="s">
+        <v>0</v>
+      </c>
+      <c r="E260" t="s">
+        <v>1</v>
+      </c>
+      <c r="F260" t="s">
+        <v>2</v>
+      </c>
+      <c r="G260" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="261" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A261">
+        <v>261</v>
+      </c>
+      <c r="B261">
+        <v>4</v>
+      </c>
+      <c r="C261">
+        <v>2</v>
+      </c>
+      <c r="D261" t="s">
+        <v>4</v>
+      </c>
+      <c r="E261" t="s">
+        <v>1</v>
+      </c>
+      <c r="F261" t="s">
+        <v>2</v>
+      </c>
+      <c r="G261" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="262" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A262">
+        <v>262</v>
+      </c>
+      <c r="B262">
+        <v>4</v>
+      </c>
+      <c r="C262">
+        <v>3</v>
+      </c>
+      <c r="D262" t="s">
+        <v>5</v>
+      </c>
+      <c r="E262" t="s">
+        <v>6</v>
+      </c>
+      <c r="F262" t="s">
+        <v>7</v>
+      </c>
+      <c r="G262" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="263" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A263">
+        <v>263</v>
+      </c>
+      <c r="B263">
+        <v>4</v>
+      </c>
+      <c r="C263">
+        <v>4</v>
+      </c>
+      <c r="D263" t="s">
+        <v>8</v>
+      </c>
+      <c r="E263" t="s">
+        <v>6</v>
+      </c>
+      <c r="F263" t="s">
+        <v>7</v>
+      </c>
+      <c r="G263" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="264" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A264">
+        <v>264</v>
+      </c>
+      <c r="B264">
+        <v>4</v>
+      </c>
+      <c r="C264">
+        <v>5</v>
+      </c>
+      <c r="D264" t="s">
         <v>266</v>
+      </c>
+      <c r="F264" t="s">
+        <v>267</v>
+      </c>
+      <c r="G264" t="s">
+        <v>268</v>
+      </c>
+    </row>
+    <row r="265" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A265">
+        <v>265</v>
+      </c>
+      <c r="B265">
+        <v>4</v>
+      </c>
+      <c r="C265">
+        <v>6</v>
+      </c>
+      <c r="D265" t="s">
+        <v>128</v>
+      </c>
+    </row>
+    <row r="266" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A266">
+        <v>266</v>
+      </c>
+      <c r="B266">
+        <v>4</v>
+      </c>
+      <c r="C266">
+        <v>7</v>
+      </c>
+      <c r="D266" t="s">
+        <v>13</v>
+      </c>
+      <c r="E266" t="s">
+        <v>129</v>
+      </c>
+      <c r="G266" t="s">
+        <v>130</v>
+      </c>
+    </row>
+    <row r="267" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A267">
+        <v>267</v>
+      </c>
+      <c r="B267">
+        <v>4</v>
+      </c>
+      <c r="C267">
+        <v>8</v>
+      </c>
+      <c r="D267" t="s">
+        <v>16</v>
+      </c>
+      <c r="F267" t="s">
+        <v>131</v>
+      </c>
+      <c r="G267" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="268" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A268">
+        <v>268</v>
+      </c>
+      <c r="B268">
+        <v>4</v>
+      </c>
+      <c r="C268">
+        <v>9</v>
+      </c>
+      <c r="D268" t="s">
+        <v>132</v>
+      </c>
+      <c r="E268" t="s">
+        <v>19</v>
+      </c>
+      <c r="F268" t="s">
+        <v>20</v>
+      </c>
+      <c r="G268" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="269" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A269">
+        <v>269</v>
+      </c>
+      <c r="B269">
+        <v>4</v>
+      </c>
+      <c r="C269">
+        <v>10</v>
+      </c>
+      <c r="D269" t="s">
+        <v>133</v>
+      </c>
+      <c r="E269" t="s">
+        <v>19</v>
+      </c>
+      <c r="F269" t="s">
+        <v>20</v>
+      </c>
+      <c r="G269" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="270" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A270">
+        <v>270</v>
+      </c>
+      <c r="B270">
+        <v>4</v>
+      </c>
+      <c r="C270">
+        <v>11</v>
+      </c>
+      <c r="D270" t="s">
+        <v>134</v>
+      </c>
+      <c r="E270" t="s">
+        <v>24</v>
+      </c>
+      <c r="F270" t="s">
+        <v>25</v>
+      </c>
+      <c r="G270" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="271" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A271">
+        <v>271</v>
+      </c>
+      <c r="B271">
+        <v>4</v>
+      </c>
+      <c r="C271">
+        <v>12</v>
+      </c>
+      <c r="D271" t="s">
+        <v>135</v>
+      </c>
+      <c r="E271" t="s">
+        <v>24</v>
+      </c>
+      <c r="F271" t="s">
+        <v>25</v>
+      </c>
+      <c r="G271" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="272" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A272">
+        <v>272</v>
+      </c>
+      <c r="B272">
+        <v>4</v>
+      </c>
+      <c r="C272">
+        <v>13</v>
+      </c>
+      <c r="D272" t="s">
+        <v>136</v>
+      </c>
+    </row>
+    <row r="273" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A273">
+        <v>273</v>
+      </c>
+      <c r="B273">
+        <v>4</v>
+      </c>
+      <c r="C273">
+        <v>14</v>
+      </c>
+      <c r="D273" t="s">
+        <v>137</v>
+      </c>
+    </row>
+    <row r="274" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A274">
+        <v>274</v>
+      </c>
+      <c r="B274">
+        <v>4</v>
+      </c>
+      <c r="C274">
+        <v>15</v>
+      </c>
+      <c r="D274" t="s">
+        <v>138</v>
+      </c>
+    </row>
+    <row r="275" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A275">
+        <v>275</v>
+      </c>
+      <c r="B275">
+        <v>4</v>
+      </c>
+      <c r="C275">
+        <v>16</v>
+      </c>
+      <c r="D275" t="s">
+        <v>139</v>
+      </c>
+    </row>
+    <row r="276" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A276">
+        <v>276</v>
+      </c>
+      <c r="B276">
+        <v>4</v>
+      </c>
+      <c r="C276">
+        <v>17</v>
+      </c>
+      <c r="D276" t="s">
+        <v>35</v>
+      </c>
+      <c r="E276" t="s">
+        <v>140</v>
+      </c>
+      <c r="G276" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="277" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A277">
+        <v>277</v>
+      </c>
+      <c r="B277">
+        <v>4</v>
+      </c>
+      <c r="C277">
+        <v>18</v>
+      </c>
+      <c r="D277" t="s">
+        <v>142</v>
+      </c>
+      <c r="F277" t="s">
+        <v>143</v>
+      </c>
+      <c r="G277" t="s">
+        <v>25</v>
+      </c>
+    </row>
+    <row r="278" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A278">
+        <v>278</v>
+      </c>
+      <c r="B278">
+        <v>4</v>
+      </c>
+      <c r="C278">
+        <v>19</v>
+      </c>
+      <c r="D278" t="s">
+        <v>40</v>
+      </c>
+      <c r="E278" t="s">
+        <v>41</v>
+      </c>
+      <c r="F278" t="s">
+        <v>42</v>
+      </c>
+      <c r="G278" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="279" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A279">
+        <v>279</v>
+      </c>
+      <c r="B279">
+        <v>4</v>
+      </c>
+      <c r="C279">
+        <v>20</v>
+      </c>
+      <c r="D279" t="s">
+        <v>43</v>
+      </c>
+      <c r="E279" t="s">
+        <v>41</v>
+      </c>
+      <c r="F279" t="s">
+        <v>42</v>
+      </c>
+      <c r="G279" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="280" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A280">
+        <v>280</v>
+      </c>
+      <c r="B280">
+        <v>4</v>
+      </c>
+      <c r="C280">
+        <v>21</v>
+      </c>
+      <c r="D280" t="s">
+        <v>44</v>
+      </c>
+      <c r="F280" t="s">
+        <v>144</v>
+      </c>
+      <c r="G280" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="281" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A281">
+        <v>281</v>
+      </c>
+      <c r="B281">
+        <v>4</v>
+      </c>
+      <c r="C281">
+        <v>22</v>
+      </c>
+      <c r="D281" t="s">
+        <v>47</v>
+      </c>
+      <c r="F281" t="s">
+        <v>48</v>
+      </c>
+      <c r="G281" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="282" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A282">
+        <v>282</v>
+      </c>
+      <c r="B282">
+        <v>4</v>
+      </c>
+      <c r="C282">
+        <v>23</v>
+      </c>
+      <c r="D282" t="s">
+        <v>49</v>
+      </c>
+      <c r="F282" t="s">
+        <v>48</v>
+      </c>
+      <c r="G282" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="283" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A283">
+        <v>283</v>
+      </c>
+      <c r="B283">
+        <v>4</v>
+      </c>
+      <c r="C283">
+        <v>24</v>
+      </c>
+      <c r="D283" t="s">
+        <v>50</v>
+      </c>
+      <c r="F283" t="s">
+        <v>48</v>
+      </c>
+      <c r="G283" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="284" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A284">
+        <v>284</v>
+      </c>
+      <c r="B284">
+        <v>4</v>
+      </c>
+      <c r="C284">
+        <v>25</v>
+      </c>
+      <c r="D284" t="s">
+        <v>51</v>
+      </c>
+      <c r="F284" t="s">
+        <v>48</v>
+      </c>
+      <c r="G284" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="285" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A285">
+        <v>285</v>
+      </c>
+      <c r="B285">
+        <v>4</v>
+      </c>
+      <c r="C285">
+        <v>26</v>
+      </c>
+      <c r="D285" t="s">
+        <v>52</v>
+      </c>
+      <c r="F285" t="s">
+        <v>53</v>
+      </c>
+      <c r="G285" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="286" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A286">
+        <v>286</v>
+      </c>
+      <c r="B286">
+        <v>4</v>
+      </c>
+      <c r="C286">
+        <v>27</v>
+      </c>
+      <c r="D286" t="s">
+        <v>54</v>
+      </c>
+      <c r="F286" t="s">
+        <v>53</v>
+      </c>
+      <c r="G286" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="287" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A287">
+        <v>287</v>
+      </c>
+      <c r="B287">
+        <v>4</v>
+      </c>
+      <c r="C287">
+        <v>28</v>
+      </c>
+      <c r="D287" t="s">
+        <v>55</v>
+      </c>
+      <c r="F287" t="s">
+        <v>53</v>
+      </c>
+      <c r="G287" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="288" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A288">
+        <v>288</v>
+      </c>
+      <c r="B288">
+        <v>4</v>
+      </c>
+      <c r="C288">
+        <v>29</v>
+      </c>
+      <c r="D288" t="s">
+        <v>56</v>
+      </c>
+      <c r="F288" t="s">
+        <v>53</v>
+      </c>
+      <c r="G288" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="289" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A289">
+        <v>289</v>
+      </c>
+      <c r="B289">
+        <v>4</v>
+      </c>
+      <c r="C289">
+        <v>30</v>
+      </c>
+      <c r="D289" t="s">
+        <v>57</v>
+      </c>
+      <c r="F289" t="s">
+        <v>53</v>
+      </c>
+      <c r="G289" t="s">
+        <v>146</v>
+      </c>
+    </row>
+    <row r="290" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A290">
+        <v>290</v>
+      </c>
+      <c r="B290">
+        <v>4</v>
+      </c>
+      <c r="C290">
+        <v>31</v>
+      </c>
+      <c r="D290" t="s">
+        <v>58</v>
+      </c>
+      <c r="F290" t="s">
+        <v>147</v>
+      </c>
+      <c r="G290" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="291" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A291">
+        <v>291</v>
+      </c>
+      <c r="B291">
+        <v>4</v>
+      </c>
+      <c r="C291">
+        <v>32</v>
+      </c>
+      <c r="D291" t="s">
+        <v>60</v>
+      </c>
+      <c r="F291" t="s">
+        <v>147</v>
+      </c>
+      <c r="G291" t="s">
+        <v>148</v>
+      </c>
+    </row>
+    <row r="292" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A292">
+        <v>292</v>
+      </c>
+      <c r="B292">
+        <v>4</v>
+      </c>
+      <c r="C292">
+        <v>33</v>
+      </c>
+      <c r="D292" t="s">
+        <v>61</v>
+      </c>
+      <c r="F292" t="s">
+        <v>149</v>
+      </c>
+      <c r="G292" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="293" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A293">
+        <v>293</v>
+      </c>
+      <c r="B293">
+        <v>4</v>
+      </c>
+      <c r="C293">
+        <v>34</v>
+      </c>
+      <c r="D293" t="s">
+        <v>63</v>
+      </c>
+      <c r="F293" t="s">
+        <v>149</v>
+      </c>
+      <c r="G293" t="s">
+        <v>269</v>
+      </c>
+    </row>
+    <row r="294" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A294">
+        <v>294</v>
+      </c>
+      <c r="B294">
+        <v>4</v>
+      </c>
+      <c r="C294">
+        <v>35</v>
+      </c>
+      <c r="D294" t="s">
+        <v>151</v>
+      </c>
+      <c r="E294" t="s">
+        <v>152</v>
+      </c>
+      <c r="F294" t="s">
+        <v>153</v>
+      </c>
+      <c r="G294" t="s">
+        <v>154</v>
+      </c>
+      <c r="H294" t="s">
+        <v>155</v>
+      </c>
+    </row>
+    <row r="295" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A295">
+        <v>295</v>
+      </c>
+      <c r="B295">
+        <v>4</v>
+      </c>
+      <c r="C295">
+        <v>36</v>
+      </c>
+      <c r="D295" t="s">
+        <v>156</v>
+      </c>
+      <c r="E295" t="s">
+        <v>152</v>
+      </c>
+      <c r="F295" t="s">
+        <v>153</v>
+      </c>
+      <c r="H295" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="296" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A296">
+        <v>296</v>
+      </c>
+      <c r="B296">
+        <v>4</v>
+      </c>
+      <c r="C296">
+        <v>37</v>
+      </c>
+      <c r="D296" t="s">
+        <v>158</v>
+      </c>
+      <c r="E296" t="s">
+        <v>152</v>
+      </c>
+      <c r="F296" t="s">
+        <v>153</v>
+      </c>
+      <c r="G296" t="s">
+        <v>154</v>
+      </c>
+      <c r="H296" t="s">
+        <v>159</v>
+      </c>
+    </row>
+    <row r="297" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A297">
+        <v>297</v>
+      </c>
+      <c r="B297">
+        <v>4</v>
+      </c>
+      <c r="C297">
+        <v>38</v>
+      </c>
+      <c r="D297" t="s">
+        <v>160</v>
+      </c>
+      <c r="E297" t="s">
+        <v>152</v>
+      </c>
+      <c r="F297" t="s">
+        <v>153</v>
+      </c>
+      <c r="H297" t="s">
+        <v>161</v>
+      </c>
+    </row>
+    <row r="298" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A298">
+        <v>298</v>
+      </c>
+      <c r="B298">
+        <v>4</v>
+      </c>
+      <c r="C298">
+        <v>39</v>
+      </c>
+      <c r="D298" t="s">
+        <v>70</v>
+      </c>
+      <c r="E298" t="s">
+        <v>6</v>
+      </c>
+      <c r="F298" t="s">
+        <v>53</v>
+      </c>
+      <c r="G298" t="s">
+        <v>162</v>
+      </c>
+    </row>
+    <row r="299" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A299">
+        <v>299</v>
+      </c>
+      <c r="B299">
+        <v>4</v>
+      </c>
+      <c r="C299">
+        <v>40</v>
+      </c>
+      <c r="D299" t="s">
+        <v>71</v>
+      </c>
+      <c r="E299" t="s">
+        <v>1</v>
+      </c>
+      <c r="F299" t="s">
+        <v>53</v>
+      </c>
+      <c r="G299" t="s">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="300" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A300">
+        <v>300</v>
+      </c>
+      <c r="B300">
+        <v>4</v>
+      </c>
+      <c r="C300">
+        <v>41</v>
+      </c>
+      <c r="D300" t="s">
+        <v>164</v>
+      </c>
+    </row>
+    <row r="301" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A301">
+        <v>301</v>
+      </c>
+      <c r="B301">
+        <v>4</v>
+      </c>
+      <c r="C301">
+        <v>42</v>
+      </c>
+      <c r="D301" t="s">
+        <v>165</v>
+      </c>
+    </row>
+    <row r="302" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A302">
+        <v>302</v>
+      </c>
+      <c r="B302">
+        <v>4</v>
+      </c>
+      <c r="C302">
+        <v>43</v>
+      </c>
+      <c r="D302" t="s">
+        <v>76</v>
+      </c>
+      <c r="E302" t="s">
+        <v>119</v>
+      </c>
+      <c r="G302" t="s">
+        <v>166</v>
+      </c>
+      <c r="H302" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="303" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A303">
+        <v>303</v>
+      </c>
+      <c r="B303">
+        <v>4</v>
+      </c>
+      <c r="C303">
+        <v>44</v>
+      </c>
+      <c r="D303" t="s">
+        <v>78</v>
+      </c>
+      <c r="E303" t="s">
+        <v>119</v>
+      </c>
+      <c r="G303" t="s">
+        <v>168</v>
+      </c>
+      <c r="H303" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="304" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A304">
+        <v>304</v>
+      </c>
+      <c r="B304">
+        <v>4</v>
+      </c>
+      <c r="C304">
+        <v>45</v>
+      </c>
+      <c r="D304" t="s">
+        <v>80</v>
+      </c>
+      <c r="E304" t="s">
+        <v>119</v>
+      </c>
+      <c r="G304" t="s">
+        <v>169</v>
+      </c>
+      <c r="H304" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="305" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A305">
+        <v>305</v>
+      </c>
+      <c r="B305">
+        <v>4</v>
+      </c>
+      <c r="C305">
+        <v>46</v>
+      </c>
+      <c r="D305" t="s">
+        <v>82</v>
+      </c>
+      <c r="E305" t="s">
+        <v>119</v>
+      </c>
+      <c r="G305" t="s">
+        <v>168</v>
+      </c>
+      <c r="H305" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="306" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A306">
+        <v>306</v>
+      </c>
+      <c r="B306">
+        <v>4</v>
+      </c>
+      <c r="C306">
+        <v>47</v>
+      </c>
+      <c r="D306" t="s">
+        <v>83</v>
+      </c>
+      <c r="E306" t="s">
+        <v>119</v>
+      </c>
+      <c r="G306" t="s">
+        <v>169</v>
+      </c>
+      <c r="H306" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="307" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A307">
+        <v>307</v>
+      </c>
+      <c r="B307">
+        <v>4</v>
+      </c>
+      <c r="C307">
+        <v>48</v>
+      </c>
+      <c r="D307" t="s">
+        <v>84</v>
+      </c>
+      <c r="E307" t="s">
+        <v>170</v>
+      </c>
+      <c r="F307" t="s">
+        <v>171</v>
+      </c>
+      <c r="G307" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="308" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A308">
+        <v>308</v>
+      </c>
+      <c r="B308">
+        <v>4</v>
+      </c>
+      <c r="C308">
+        <v>49</v>
+      </c>
+      <c r="D308" t="s">
+        <v>86</v>
+      </c>
+      <c r="E308" t="s">
+        <v>170</v>
+      </c>
+      <c r="F308" t="s">
+        <v>171</v>
+      </c>
+      <c r="G308" t="s">
+        <v>172</v>
+      </c>
+    </row>
+    <row r="309" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A309">
+        <v>309</v>
+      </c>
+      <c r="B309">
+        <v>4</v>
+      </c>
+      <c r="C309">
+        <v>50</v>
+      </c>
+      <c r="D309" t="s">
+        <v>173</v>
+      </c>
+      <c r="E309" t="s">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="310" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A310">
+        <v>310</v>
+      </c>
+      <c r="B310">
+        <v>4</v>
+      </c>
+      <c r="C310">
+        <v>51</v>
+      </c>
+      <c r="D310" t="s">
+        <v>88</v>
+      </c>
+      <c r="E310" t="s">
+        <v>175</v>
+      </c>
+      <c r="F310" t="s">
+        <v>176</v>
+      </c>
+      <c r="G310" t="s">
+        <v>177</v>
+      </c>
+      <c r="H310" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="311" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A311">
+        <v>311</v>
+      </c>
+      <c r="B311">
+        <v>4</v>
+      </c>
+      <c r="C311">
+        <v>52</v>
+      </c>
+      <c r="D311" t="s">
+        <v>91</v>
+      </c>
+    </row>
+    <row r="312" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A312">
+        <v>312</v>
+      </c>
+      <c r="B312">
+        <v>4</v>
+      </c>
+      <c r="C312">
+        <v>53</v>
+      </c>
+      <c r="D312" t="s">
+        <v>92</v>
+      </c>
+    </row>
+    <row r="313" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A313">
+        <v>313</v>
+      </c>
+      <c r="B313">
+        <v>4</v>
+      </c>
+      <c r="C313">
+        <v>54</v>
+      </c>
+      <c r="D313" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="314" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A314">
+        <v>314</v>
+      </c>
+      <c r="B314">
+        <v>4</v>
+      </c>
+      <c r="C314">
+        <v>55</v>
+      </c>
+      <c r="D314" t="s">
+        <v>179</v>
+      </c>
+      <c r="E314" t="s">
+        <v>180</v>
+      </c>
+      <c r="G314" t="s">
+        <v>181</v>
+      </c>
+    </row>
+    <row r="315" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A315">
+        <v>315</v>
+      </c>
+      <c r="B315">
+        <v>4</v>
+      </c>
+      <c r="C315">
+        <v>56</v>
+      </c>
+      <c r="D315" t="s">
+        <v>182</v>
+      </c>
+      <c r="E315" t="s">
+        <v>183</v>
+      </c>
+      <c r="F315" t="s">
+        <v>184</v>
+      </c>
+      <c r="G315" t="s">
+        <v>183</v>
+      </c>
+      <c r="H315" t="s">
+        <v>185</v>
+      </c>
+    </row>
+    <row r="316" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A316">
+        <v>316</v>
+      </c>
+      <c r="B316">
+        <v>4</v>
+      </c>
+      <c r="C316">
+        <v>57</v>
+      </c>
+      <c r="D316" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="317" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A317">
+        <v>317</v>
+      </c>
+      <c r="B317">
+        <v>4</v>
+      </c>
+      <c r="C317">
+        <v>58</v>
+      </c>
+      <c r="D317" t="s">
+        <v>187</v>
+      </c>
+    </row>
+    <row r="318" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A318">
+        <v>318</v>
+      </c>
+      <c r="B318">
+        <v>4</v>
+      </c>
+      <c r="C318">
+        <v>59</v>
+      </c>
+      <c r="D318" t="s">
+        <v>188</v>
+      </c>
+      <c r="E318" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="319" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A319">
+        <v>319</v>
+      </c>
+      <c r="B319">
+        <v>4</v>
+      </c>
+      <c r="C319">
+        <v>60</v>
+      </c>
+      <c r="D319" t="s">
+        <v>190</v>
+      </c>
+      <c r="F319" t="s">
+        <v>191</v>
+      </c>
+      <c r="G319" t="s">
+        <v>192</v>
+      </c>
+    </row>
+    <row r="320" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A320">
+        <v>320</v>
+      </c>
+      <c r="B320">
+        <v>4</v>
+      </c>
+      <c r="C320">
+        <v>61</v>
+      </c>
+      <c r="D320" t="s">
+        <v>105</v>
+      </c>
+      <c r="E320" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="321" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A321">
+        <v>321</v>
+      </c>
+      <c r="B321">
+        <v>4</v>
+      </c>
+      <c r="C321">
+        <v>62</v>
+      </c>
+      <c r="D321" t="s">
+        <v>106</v>
+      </c>
+      <c r="E321" t="s">
+        <v>189</v>
+      </c>
+    </row>
+    <row r="322" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A322">
+        <v>322</v>
+      </c>
+      <c r="B322">
+        <v>4</v>
+      </c>
+      <c r="C322">
+        <v>63</v>
+      </c>
+      <c r="D322" t="s">
+        <v>107</v>
+      </c>
+      <c r="E322" t="s">
+        <v>41</v>
+      </c>
+      <c r="F322" t="s">
+        <v>42</v>
+      </c>
+      <c r="G322" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="323" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A323">
+        <v>323</v>
+      </c>
+      <c r="B323">
+        <v>4</v>
+      </c>
+      <c r="C323">
+        <v>64</v>
+      </c>
+      <c r="D323" t="s">
+        <v>109</v>
+      </c>
+      <c r="E323" t="s">
+        <v>41</v>
+      </c>
+      <c r="F323" t="s">
+        <v>42</v>
+      </c>
+      <c r="G323" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="324" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A324">
+        <v>324</v>
+      </c>
+      <c r="B324">
+        <v>4</v>
+      </c>
+      <c r="C324">
+        <v>65</v>
+      </c>
+      <c r="D324" t="s">
+        <v>110</v>
+      </c>
+      <c r="G324" t="s">
+        <v>141</v>
+      </c>
+    </row>
+    <row r="325" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A325">
+        <v>325</v>
+      </c>
+      <c r="B325">
+        <v>4</v>
+      </c>
+      <c r="C325">
+        <v>66</v>
+      </c>
+      <c r="D325" t="s">
+        <v>112</v>
+      </c>
+      <c r="F325" t="s">
+        <v>42</v>
+      </c>
+      <c r="G325" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="326" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A326">
+        <v>326</v>
+      </c>
+      <c r="B326">
+        <v>4</v>
+      </c>
+      <c r="C326">
+        <v>67</v>
+      </c>
+      <c r="D326" t="s">
+        <v>114</v>
+      </c>
+    </row>
+    <row r="327" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A327">
+        <v>327</v>
+      </c>
+      <c r="B327">
+        <v>4</v>
+      </c>
+      <c r="C327">
+        <v>68</v>
+      </c>
+      <c r="D327" t="s">
+        <v>116</v>
+      </c>
+      <c r="E327" t="s">
+        <v>193</v>
+      </c>
+      <c r="G327" t="s">
+        <v>194</v>
+      </c>
+    </row>
+    <row r="328" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A328">
+        <v>328</v>
+      </c>
+      <c r="B328">
+        <v>4</v>
+      </c>
+      <c r="C328">
+        <v>69</v>
+      </c>
+      <c r="D328" t="s">
+        <v>195</v>
+      </c>
+      <c r="E328" t="s">
+        <v>119</v>
+      </c>
+      <c r="G328" t="s">
+        <v>196</v>
+      </c>
+      <c r="H328" t="s">
+        <v>167</v>
+      </c>
+    </row>
+    <row r="329" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A329">
+        <v>329</v>
+      </c>
+      <c r="B329">
+        <v>4</v>
+      </c>
+      <c r="C329">
+        <v>70</v>
+      </c>
+      <c r="D329" t="s">
+        <v>197</v>
+      </c>
+      <c r="E329" t="s">
+        <v>198</v>
+      </c>
+      <c r="F329" t="s">
+        <v>163</v>
+      </c>
+      <c r="G329" t="s">
+        <v>199</v>
+      </c>
+    </row>
+    <row r="330" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A330">
+        <v>330</v>
+      </c>
+      <c r="B330">
+        <v>4</v>
+      </c>
+      <c r="C330">
+        <v>71</v>
+      </c>
+      <c r="D330" t="s">
+        <v>200</v>
+      </c>
+      <c r="E330" t="s">
+        <v>201</v>
+      </c>
+      <c r="G330" t="s">
+        <v>202</v>
+      </c>
+      <c r="H330" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="331" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A331">
+        <v>331</v>
+      </c>
+      <c r="B331">
+        <v>4</v>
+      </c>
+      <c r="C331">
+        <v>72</v>
+      </c>
+      <c r="D331" t="s">
+        <v>204</v>
+      </c>
+      <c r="E331" t="s">
+        <v>201</v>
+      </c>
+      <c r="G331" t="s">
+        <v>202</v>
+      </c>
+      <c r="H331" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="332" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A332">
+        <v>332</v>
+      </c>
+      <c r="B332">
+        <v>4</v>
+      </c>
+      <c r="C332">
+        <v>73</v>
+      </c>
+      <c r="D332" t="s">
+        <v>205</v>
+      </c>
+      <c r="E332" t="s">
+        <v>201</v>
+      </c>
+      <c r="G332" t="s">
+        <v>202</v>
+      </c>
+      <c r="H332" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="333" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A333">
+        <v>333</v>
+      </c>
+      <c r="B333">
+        <v>4</v>
+      </c>
+      <c r="C333">
+        <v>74</v>
+      </c>
+      <c r="D333" t="s">
+        <v>206</v>
+      </c>
+      <c r="E333" t="s">
+        <v>201</v>
+      </c>
+      <c r="G333" t="s">
+        <v>202</v>
+      </c>
+      <c r="H333" t="s">
+        <v>203</v>
+      </c>
+    </row>
+    <row r="334" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A334">
+        <v>334</v>
+      </c>
+      <c r="B334">
+        <v>4</v>
+      </c>
+      <c r="C334">
+        <v>128</v>
+      </c>
+      <c r="D334" t="s">
+        <v>121</v>
+      </c>
+      <c r="G334" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="335" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A335">
+        <v>335</v>
+      </c>
+      <c r="B335">
+        <v>4</v>
+      </c>
+      <c r="C335">
+        <v>129</v>
+      </c>
+      <c r="D335" t="s">
+        <v>123</v>
+      </c>
+      <c r="G335" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="336" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A336">
+        <v>336</v>
+      </c>
+      <c r="B336">
+        <v>4</v>
+      </c>
+      <c r="C336">
+        <v>130</v>
+      </c>
+      <c r="D336" t="s">
+        <v>124</v>
+      </c>
+      <c r="G336" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="337" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A337">
+        <v>337</v>
+      </c>
+      <c r="B337">
+        <v>4</v>
+      </c>
+      <c r="C337">
+        <v>131</v>
+      </c>
+      <c r="D337" t="s">
+        <v>125</v>
+      </c>
+      <c r="G337" t="s">
+        <v>207</v>
+      </c>
+    </row>
+    <row r="338" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A338">
+        <v>338</v>
+      </c>
+      <c r="B338">
+        <v>4</v>
+      </c>
+      <c r="C338">
+        <v>75</v>
+      </c>
+      <c r="D338" t="s">
+        <v>208</v>
+      </c>
+      <c r="E338" t="s">
+        <v>209</v>
+      </c>
+      <c r="F338" t="s">
+        <v>210</v>
+      </c>
+      <c r="G338" t="s">
+        <v>210</v>
+      </c>
+    </row>
+    <row r="339" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A339">
+        <v>339</v>
+      </c>
+      <c r="B339">
+        <v>4</v>
+      </c>
+      <c r="C339">
+        <v>76</v>
+      </c>
+      <c r="D339" t="s">
+        <v>211</v>
+      </c>
+    </row>
+    <row r="340" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A340">
+        <v>340</v>
+      </c>
+      <c r="B340">
+        <v>4</v>
+      </c>
+      <c r="C340">
+        <v>77</v>
+      </c>
+      <c r="D340" t="s">
+        <v>212</v>
+      </c>
+    </row>
+    <row r="341" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A341">
+        <v>341</v>
+      </c>
+      <c r="B341">
+        <v>4</v>
+      </c>
+      <c r="C341">
+        <v>78</v>
+      </c>
+      <c r="D341" t="s">
+        <v>213</v>
+      </c>
+      <c r="F341" t="s">
+        <v>214</v>
+      </c>
+      <c r="G341" t="s">
+        <v>215</v>
+      </c>
+    </row>
+    <row r="342" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A342">
+        <v>342</v>
+      </c>
+      <c r="B342">
+        <v>4</v>
+      </c>
+      <c r="C342">
+        <v>79</v>
+      </c>
+      <c r="D342" t="s">
+        <v>216</v>
+      </c>
+      <c r="E342" t="s">
+        <v>183</v>
+      </c>
+      <c r="G342" t="s">
+        <v>217</v>
+      </c>
+      <c r="H342" t="s">
+        <v>218</v>
+      </c>
+    </row>
+    <row r="343" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A343">
+        <v>343</v>
+      </c>
+      <c r="B343">
+        <v>4</v>
+      </c>
+      <c r="C343">
+        <v>80</v>
+      </c>
+      <c r="D343" t="s">
+        <v>219</v>
+      </c>
+    </row>
+    <row r="344" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A344">
+        <v>344</v>
+      </c>
+      <c r="B344">
+        <v>4</v>
+      </c>
+      <c r="C344">
+        <v>81</v>
+      </c>
+      <c r="D344" t="s">
+        <v>220</v>
+      </c>
+      <c r="E344" t="s">
+        <v>221</v>
+      </c>
+      <c r="H344" t="s">
+        <v>222</v>
+      </c>
+    </row>
+    <row r="345" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A345">
+        <v>345</v>
+      </c>
+      <c r="B345">
+        <v>4</v>
+      </c>
+      <c r="C345">
+        <v>82</v>
+      </c>
+      <c r="D345" t="s">
+        <v>223</v>
+      </c>
+      <c r="E345" t="s">
+        <v>224</v>
+      </c>
+      <c r="G345" t="s">
+        <v>209</v>
+      </c>
+    </row>
+    <row r="346" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A346">
+        <v>346</v>
+      </c>
+      <c r="B346">
+        <v>4</v>
+      </c>
+      <c r="C346">
+        <v>83</v>
+      </c>
+      <c r="D346" t="s">
+        <v>225</v>
+      </c>
+      <c r="E346" t="s">
+        <v>226</v>
+      </c>
+      <c r="F346" t="s">
+        <v>227</v>
+      </c>
+      <c r="G346" t="s">
+        <v>228</v>
+      </c>
+    </row>
+    <row r="347" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A347">
+        <v>347</v>
+      </c>
+      <c r="B347">
+        <v>4</v>
+      </c>
+      <c r="C347">
+        <v>84</v>
+      </c>
+      <c r="D347" t="s">
+        <v>229</v>
+      </c>
+      <c r="G347" t="s">
+        <v>230</v>
+      </c>
+      <c r="H347" t="s">
+        <v>231</v>
+      </c>
+    </row>
+    <row r="348" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A348">
+        <v>348</v>
+      </c>
+      <c r="B348">
+        <v>4</v>
+      </c>
+      <c r="C348">
+        <v>85</v>
+      </c>
+      <c r="D348" t="s">
+        <v>232</v>
+      </c>
+      <c r="F348" t="s">
+        <v>230</v>
+      </c>
+      <c r="H348" t="s">
+        <v>233</v>
+      </c>
+    </row>
+    <row r="349" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A349">
+        <v>349</v>
+      </c>
+      <c r="B349">
+        <v>4</v>
+      </c>
+      <c r="C349">
+        <v>86</v>
+      </c>
+      <c r="D349" t="s">
+        <v>234</v>
+      </c>
+      <c r="G349" t="s">
+        <v>224</v>
+      </c>
+    </row>
+    <row r="350" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A350">
+        <v>350</v>
+      </c>
+      <c r="B350">
+        <v>4</v>
+      </c>
+      <c r="C350">
+        <v>87</v>
+      </c>
+      <c r="D350" t="s">
+        <v>235</v>
+      </c>
+      <c r="F350" t="s">
+        <v>236</v>
+      </c>
+      <c r="G350" t="s">
+        <v>237</v>
+      </c>
+    </row>
+    <row r="351" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A351">
+        <v>351</v>
+      </c>
+      <c r="B351">
+        <v>4</v>
+      </c>
+      <c r="C351">
+        <v>88</v>
+      </c>
+      <c r="D351" t="s">
+        <v>238</v>
+      </c>
+      <c r="E351" t="s">
+        <v>239</v>
+      </c>
+      <c r="F351" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="352" spans="1:8" x14ac:dyDescent="0.2">
+      <c r="A352">
+        <v>352</v>
+      </c>
+      <c r="B352">
+        <v>4</v>
+      </c>
+      <c r="C352">
+        <v>89</v>
+      </c>
+      <c r="D352" t="s">
+        <v>241</v>
+      </c>
+      <c r="E352" t="s">
+        <v>239</v>
+      </c>
+      <c r="F352" t="s">
+        <v>240</v>
+      </c>
+    </row>
+    <row r="353" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A353">
+        <v>353</v>
+      </c>
+      <c r="B353">
+        <v>4</v>
+      </c>
+      <c r="C353">
+        <v>90</v>
+      </c>
+      <c r="D353" t="s">
+        <v>270</v>
+      </c>
+      <c r="E353" t="s">
+        <v>271</v>
+      </c>
+      <c r="F353" t="s">
+        <v>239</v>
+      </c>
+      <c r="G353" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="354" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A354">
+        <v>354</v>
+      </c>
+      <c r="B354">
+        <v>4</v>
+      </c>
+      <c r="C354">
+        <v>91</v>
+      </c>
+      <c r="D354" t="s">
+        <v>272</v>
+      </c>
+      <c r="E354" t="s">
+        <v>273</v>
+      </c>
+      <c r="F354" t="s">
+        <v>274</v>
+      </c>
+    </row>
+    <row r="355" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A355">
+        <v>355</v>
+      </c>
+      <c r="B355">
+        <v>4</v>
+      </c>
+      <c r="C355">
+        <v>92</v>
+      </c>
+      <c r="D355" t="s">
+        <v>275</v>
+      </c>
+      <c r="E355" t="s">
+        <v>276</v>
+      </c>
+      <c r="F355" t="s">
+        <v>277</v>
+      </c>
+    </row>
+    <row r="356" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A356">
+        <v>356</v>
+      </c>
+      <c r="B356">
+        <v>4</v>
+      </c>
+      <c r="C356">
+        <v>93</v>
+      </c>
+      <c r="D356" t="s">
+        <v>278</v>
+      </c>
+      <c r="E356" t="s">
+        <v>279</v>
+      </c>
+    </row>
+    <row r="357" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A357">
+        <v>357</v>
+      </c>
+      <c r="B357">
+        <v>4</v>
+      </c>
+      <c r="C357">
+        <v>94</v>
+      </c>
+      <c r="D357" t="s">
+        <v>280</v>
+      </c>
+      <c r="E357" t="s">
+        <v>281</v>
+      </c>
+      <c r="F357" t="s">
+        <v>53</v>
+      </c>
+    </row>
+    <row r="358" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A358">
+        <v>358</v>
+      </c>
+      <c r="B358">
+        <v>4</v>
+      </c>
+      <c r="C358">
+        <v>95</v>
+      </c>
+      <c r="D358" t="s">
+        <v>282</v>
+      </c>
+    </row>
+    <row r="359" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A359">
+        <v>359</v>
+      </c>
+      <c r="B359">
+        <v>4</v>
+      </c>
+      <c r="C359">
+        <v>96</v>
+      </c>
+      <c r="D359" t="s">
+        <v>283</v>
+      </c>
+    </row>
+    <row r="360" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A360">
+        <v>360</v>
+      </c>
+      <c r="B360">
+        <v>4</v>
+      </c>
+      <c r="C360">
+        <v>97</v>
+      </c>
+      <c r="D360" t="s">
+        <v>284</v>
+      </c>
+      <c r="F360" t="s">
+        <v>48</v>
+      </c>
+      <c r="G360" t="s">
+        <v>145</v>
+      </c>
+    </row>
+    <row r="361" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A361">
+        <v>361</v>
+      </c>
+      <c r="B361">
+        <v>4</v>
+      </c>
+      <c r="C361">
+        <v>98</v>
+      </c>
+      <c r="D361" t="s">
+        <v>285</v>
+      </c>
+      <c r="E361" t="s">
+        <v>6</v>
+      </c>
+      <c r="F361" t="s">
+        <v>7</v>
+      </c>
+      <c r="G361" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="362" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A362">
+        <v>362</v>
+      </c>
+      <c r="B362">
+        <v>4</v>
+      </c>
+      <c r="C362">
+        <v>99</v>
+      </c>
+      <c r="D362" t="s">
+        <v>286</v>
+      </c>
+      <c r="E362" t="s">
+        <v>19</v>
+      </c>
+      <c r="F362" t="s">
+        <v>20</v>
+      </c>
+      <c r="G362" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="363" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A363">
+        <v>363</v>
+      </c>
+      <c r="B363">
+        <v>4</v>
+      </c>
+      <c r="C363">
+        <v>100</v>
+      </c>
+      <c r="D363" t="s">
+        <v>287</v>
+      </c>
+      <c r="E363" t="s">
+        <v>24</v>
+      </c>
+      <c r="F363" t="s">
+        <v>25</v>
+      </c>
+      <c r="G363" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="364" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A364">
+        <v>364</v>
+      </c>
+      <c r="B364">
+        <v>4</v>
+      </c>
+      <c r="C364">
+        <v>101</v>
+      </c>
+      <c r="D364" t="s">
+        <v>288</v>
+      </c>
+      <c r="E364" t="s">
+        <v>19</v>
+      </c>
+      <c r="F364" t="s">
+        <v>20</v>
+      </c>
+      <c r="G364" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="365" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A365">
+        <v>365</v>
+      </c>
+      <c r="B365">
+        <v>4</v>
+      </c>
+      <c r="C365">
+        <v>102</v>
+      </c>
+      <c r="D365" t="s">
+        <v>289</v>
+      </c>
+      <c r="E365" t="s">
+        <v>19</v>
+      </c>
+      <c r="F365" t="s">
+        <v>20</v>
+      </c>
+      <c r="G365" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="366" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A366">
+        <v>366</v>
+      </c>
+      <c r="B366">
+        <v>4</v>
+      </c>
+      <c r="C366">
+        <v>103</v>
+      </c>
+      <c r="D366" t="s">
+        <v>290</v>
+      </c>
+    </row>
+    <row r="367" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A367">
+        <v>367</v>
+      </c>
+      <c r="B367">
+        <v>4</v>
+      </c>
+      <c r="C367">
+        <v>104</v>
+      </c>
+      <c r="D367" t="s">
+        <v>291</v>
+      </c>
+      <c r="E367" t="s">
+        <v>1</v>
+      </c>
+      <c r="F367" t="s">
+        <v>2</v>
+      </c>
+      <c r="G367" t="s">
+        <v>3</v>
+      </c>
+    </row>
+    <row r="368" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A368">
+        <v>368</v>
+      </c>
+      <c r="B368">
+        <v>4</v>
+      </c>
+      <c r="C368">
+        <v>105</v>
+      </c>
+      <c r="D368" t="s">
+        <v>292</v>
+      </c>
+      <c r="E368" t="s">
+        <v>19</v>
+      </c>
+      <c r="F368" t="s">
+        <v>20</v>
+      </c>
+      <c r="G368" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="369" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A369">
+        <v>369</v>
+      </c>
+      <c r="B369">
+        <v>4</v>
+      </c>
+      <c r="C369">
+        <v>106</v>
+      </c>
+      <c r="D369" t="s">
+        <v>293</v>
+      </c>
+      <c r="E369" t="s">
+        <v>24</v>
+      </c>
+      <c r="F369" t="s">
+        <v>25</v>
+      </c>
+      <c r="G369" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="370" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A370">
+        <v>370</v>
+      </c>
+      <c r="B370">
+        <v>4</v>
+      </c>
+      <c r="C370">
+        <v>107</v>
+      </c>
+      <c r="D370" t="s">
+        <v>294</v>
+      </c>
+      <c r="E370" t="s">
+        <v>19</v>
+      </c>
+      <c r="F370" t="s">
+        <v>20</v>
+      </c>
+      <c r="G370" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="371" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A371">
+        <v>371</v>
+      </c>
+      <c r="B371">
+        <v>4</v>
+      </c>
+      <c r="C371">
+        <v>108</v>
+      </c>
+      <c r="D371" t="s">
+        <v>295</v>
+      </c>
+      <c r="E371" t="s">
+        <v>24</v>
+      </c>
+      <c r="F371" t="s">
+        <v>25</v>
+      </c>
+      <c r="G371" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="372" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A372">
+        <v>372</v>
+      </c>
+      <c r="B372">
+        <v>4</v>
+      </c>
+      <c r="C372">
+        <v>109</v>
+      </c>
+      <c r="D372" t="s">
+        <v>296</v>
+      </c>
+      <c r="E372" t="s">
+        <v>24</v>
+      </c>
+      <c r="F372" t="s">
+        <v>25</v>
+      </c>
+      <c r="G372" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="373" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A373">
+        <v>373</v>
+      </c>
+      <c r="B373">
+        <v>4</v>
+      </c>
+      <c r="C373">
+        <v>110</v>
+      </c>
+      <c r="D373" t="s">
+        <v>297</v>
+      </c>
+      <c r="E373" t="s">
+        <v>24</v>
+      </c>
+      <c r="F373" t="s">
+        <v>25</v>
+      </c>
+      <c r="G373" t="s">
+        <v>21</v>
+      </c>
+    </row>
+    <row r="374" spans="1:7" x14ac:dyDescent="0.2">
+      <c r="A374">
+        <v>374</v>
+      </c>
+      <c r="B374">
+        <v>4</v>
+      </c>
+      <c r="C374">
+        <v>111</v>
+      </c>
+      <c r="D374" t="s">
+        <v>298</v>
+      </c>
+      <c r="F374" t="s">
+        <v>20</v>
+      </c>
+      <c r="G374" t="s">
+        <v>25</v>
       </c>
     </row>
   </sheetData>
